--- a/Assets/Excel/StageWaveSO.xlsx
+++ b/Assets/Excel/StageWaveSO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UNITY\UNITY_PROJECT\TeamProject_CheerUpMyHero\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{717E2324-8FF1-402F-BA7C-2736683513C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34D40EB9-419B-4F60-855F-0DC187E2E4FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19200" yWindow="0" windowWidth="19200" windowHeight="21000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1125" yWindow="2805" windowWidth="28800" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="stageWaveData1" sheetId="1" r:id="rId1"/>

--- a/Assets/Excel/StageWaveSO.xlsx
+++ b/Assets/Excel/StageWaveSO.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UNITY\UNITY_PROJECT\TeamProject_CheerUpMyHero\Assets\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\TeamProject_CheerUpMyHero\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34D40EB9-419B-4F60-855F-0DC187E2E4FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B40EDA17-0CD9-4416-B934-1768A93757E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1125" yWindow="2805" windowWidth="28800" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="stageWaveData1" sheetId="1" r:id="rId1"/>
     <sheet name="stageWaveData2" sheetId="3" r:id="rId2"/>
+    <sheet name="stageWaveData3" sheetId="4" r:id="rId3"/>
+    <sheet name="stageWaveData4" sheetId="5" r:id="rId4"/>
+    <sheet name="stageWaveData5" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,8 +31,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="705" uniqueCount="43">
   <si>
     <t>idNumber</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -106,6 +107,69 @@
   </si>
   <si>
     <t>EnemyUnit17</t>
+  </si>
+  <si>
+    <t>EnemyUnit21</t>
+  </si>
+  <si>
+    <t>EnemyUnit22</t>
+  </si>
+  <si>
+    <t>EnemyUnit23</t>
+  </si>
+  <si>
+    <t>EnemyUnit24</t>
+  </si>
+  <si>
+    <t>EnemyUnit25</t>
+  </si>
+  <si>
+    <t>EnemyUnit26</t>
+  </si>
+  <si>
+    <t>EnemyUnit27</t>
+  </si>
+  <si>
+    <t>EnemyUnit31</t>
+  </si>
+  <si>
+    <t>EnemyUnit32</t>
+  </si>
+  <si>
+    <t>EnemyUnit33</t>
+  </si>
+  <si>
+    <t>EnemyUnit34</t>
+  </si>
+  <si>
+    <t>EnemyUnit35</t>
+  </si>
+  <si>
+    <t>EnemyUnit36</t>
+  </si>
+  <si>
+    <t>EnemyUnit37</t>
+  </si>
+  <si>
+    <t>EnemyUnit41</t>
+  </si>
+  <si>
+    <t>EnemyUnit42</t>
+  </si>
+  <si>
+    <t>EnemyUnit43</t>
+  </si>
+  <si>
+    <t>EnemyUnit44</t>
+  </si>
+  <si>
+    <t>EnemyUnit45</t>
+  </si>
+  <si>
+    <t>EnemyUnit46</t>
+  </si>
+  <si>
+    <t>EnemyUnit47</t>
   </si>
 </sst>
 </file>
@@ -3318,7 +3382,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>16</v>
@@ -3338,7 +3402,7 @@
         <v>1</v>
       </c>
       <c r="C8" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>15</v>
@@ -3358,7 +3422,7 @@
         <v>1</v>
       </c>
       <c r="C9" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>16</v>
@@ -3518,7 +3582,7 @@
         <v>2</v>
       </c>
       <c r="C17" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>16</v>
@@ -3538,7 +3602,7 @@
         <v>2</v>
       </c>
       <c r="C18" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>15</v>
@@ -3558,7 +3622,7 @@
         <v>2</v>
       </c>
       <c r="C19" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>16</v>
@@ -3718,7 +3782,7 @@
         <v>3</v>
       </c>
       <c r="C27" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>16</v>
@@ -3738,7 +3802,7 @@
         <v>3</v>
       </c>
       <c r="C28" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>15</v>
@@ -3758,7 +3822,7 @@
         <v>3</v>
       </c>
       <c r="C29" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>16</v>
@@ -5902,6 +5966,8217 @@
       </c>
       <c r="D136" s="2" t="s">
         <v>21</v>
+      </c>
+      <c r="E136" s="2">
+        <v>8</v>
+      </c>
+      <c r="F136" s="2">
+        <v>120</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6195BD7A-C072-4C92-A7D6-BEB86F28D312}">
+  <dimension ref="A1:F136"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>30000001</v>
+      </c>
+      <c r="B2" s="2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="2">
+        <v>8</v>
+      </c>
+      <c r="F2" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>30000002</v>
+      </c>
+      <c r="B3" s="2">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="2">
+        <v>8</v>
+      </c>
+      <c r="F3" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>30000003</v>
+      </c>
+      <c r="B4" s="2">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2">
+        <v>2</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="2">
+        <v>8</v>
+      </c>
+      <c r="F4" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>30000004</v>
+      </c>
+      <c r="B5" s="2">
+        <v>1</v>
+      </c>
+      <c r="C5" s="2">
+        <v>2</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="2">
+        <v>8</v>
+      </c>
+      <c r="F5" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>30000005</v>
+      </c>
+      <c r="B6" s="2">
+        <v>1</v>
+      </c>
+      <c r="C6" s="2">
+        <v>3</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="2">
+        <v>16</v>
+      </c>
+      <c r="F6" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>30000006</v>
+      </c>
+      <c r="B7" s="2">
+        <v>1</v>
+      </c>
+      <c r="C7" s="2">
+        <v>3</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="2">
+        <v>16</v>
+      </c>
+      <c r="F7" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>30000007</v>
+      </c>
+      <c r="B8" s="2">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2">
+        <v>4</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="2">
+        <v>16</v>
+      </c>
+      <c r="F8" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>30000008</v>
+      </c>
+      <c r="B9" s="2">
+        <v>1</v>
+      </c>
+      <c r="C9" s="2">
+        <v>4</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="2">
+        <v>16</v>
+      </c>
+      <c r="F9" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>30000009</v>
+      </c>
+      <c r="B10" s="2">
+        <v>1</v>
+      </c>
+      <c r="C10" s="2">
+        <v>5</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="2">
+        <v>24</v>
+      </c>
+      <c r="F10" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>30000010</v>
+      </c>
+      <c r="B11" s="2">
+        <v>1</v>
+      </c>
+      <c r="C11" s="2">
+        <v>5</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="2">
+        <v>24</v>
+      </c>
+      <c r="F11" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>30000011</v>
+      </c>
+      <c r="B12" s="1">
+        <v>2</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="1">
+        <v>8</v>
+      </c>
+      <c r="F12" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>30000012</v>
+      </c>
+      <c r="B13" s="1">
+        <v>2</v>
+      </c>
+      <c r="C13" s="1">
+        <v>1</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="1">
+        <v>8</v>
+      </c>
+      <c r="F13" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <v>30000013</v>
+      </c>
+      <c r="B14" s="1">
+        <v>2</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="1">
+        <v>8</v>
+      </c>
+      <c r="F14" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>30000014</v>
+      </c>
+      <c r="B15" s="1">
+        <v>2</v>
+      </c>
+      <c r="C15" s="1">
+        <v>2</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="1">
+        <v>8</v>
+      </c>
+      <c r="F15" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>30000015</v>
+      </c>
+      <c r="B16" s="1">
+        <v>2</v>
+      </c>
+      <c r="C16" s="1">
+        <v>3</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" s="1">
+        <v>16</v>
+      </c>
+      <c r="F16" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>30000016</v>
+      </c>
+      <c r="B17" s="1">
+        <v>2</v>
+      </c>
+      <c r="C17" s="1">
+        <v>3</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="1">
+        <v>16</v>
+      </c>
+      <c r="F17" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>30000017</v>
+      </c>
+      <c r="B18" s="1">
+        <v>2</v>
+      </c>
+      <c r="C18" s="1">
+        <v>4</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="1">
+        <v>16</v>
+      </c>
+      <c r="F18" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <v>30000018</v>
+      </c>
+      <c r="B19" s="1">
+        <v>2</v>
+      </c>
+      <c r="C19" s="1">
+        <v>4</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="1">
+        <v>16</v>
+      </c>
+      <c r="F19" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <v>30000019</v>
+      </c>
+      <c r="B20" s="1">
+        <v>2</v>
+      </c>
+      <c r="C20" s="1">
+        <v>5</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" s="1">
+        <v>24</v>
+      </c>
+      <c r="F20" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <v>30000020</v>
+      </c>
+      <c r="B21" s="1">
+        <v>2</v>
+      </c>
+      <c r="C21" s="1">
+        <v>5</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" s="1">
+        <v>24</v>
+      </c>
+      <c r="F21" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="2">
+        <v>30000021</v>
+      </c>
+      <c r="B22" s="2">
+        <v>3</v>
+      </c>
+      <c r="C22" s="2">
+        <v>1</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E22" s="2">
+        <v>8</v>
+      </c>
+      <c r="F22" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="2">
+        <v>30000022</v>
+      </c>
+      <c r="B23" s="2">
+        <v>3</v>
+      </c>
+      <c r="C23" s="2">
+        <v>1</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E23" s="2">
+        <v>8</v>
+      </c>
+      <c r="F23" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="2">
+        <v>30000023</v>
+      </c>
+      <c r="B24" s="2">
+        <v>3</v>
+      </c>
+      <c r="C24" s="2">
+        <v>2</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E24" s="2">
+        <v>8</v>
+      </c>
+      <c r="F24" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="2">
+        <v>30000024</v>
+      </c>
+      <c r="B25" s="2">
+        <v>3</v>
+      </c>
+      <c r="C25" s="2">
+        <v>2</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E25" s="2">
+        <v>8</v>
+      </c>
+      <c r="F25" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="2">
+        <v>30000025</v>
+      </c>
+      <c r="B26" s="2">
+        <v>3</v>
+      </c>
+      <c r="C26" s="2">
+        <v>3</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" s="2">
+        <v>16</v>
+      </c>
+      <c r="F26" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="2">
+        <v>30000026</v>
+      </c>
+      <c r="B27" s="2">
+        <v>3</v>
+      </c>
+      <c r="C27" s="2">
+        <v>3</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E27" s="2">
+        <v>16</v>
+      </c>
+      <c r="F27" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="2">
+        <v>30000027</v>
+      </c>
+      <c r="B28" s="2">
+        <v>3</v>
+      </c>
+      <c r="C28" s="2">
+        <v>4</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E28" s="2">
+        <v>16</v>
+      </c>
+      <c r="F28" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="2">
+        <v>30000028</v>
+      </c>
+      <c r="B29" s="2">
+        <v>3</v>
+      </c>
+      <c r="C29" s="2">
+        <v>4</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E29" s="2">
+        <v>16</v>
+      </c>
+      <c r="F29" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="2">
+        <v>30000029</v>
+      </c>
+      <c r="B30" s="2">
+        <v>3</v>
+      </c>
+      <c r="C30" s="2">
+        <v>5</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E30" s="2">
+        <v>24</v>
+      </c>
+      <c r="F30" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="2">
+        <v>30000030</v>
+      </c>
+      <c r="B31" s="2">
+        <v>3</v>
+      </c>
+      <c r="C31" s="2">
+        <v>5</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E31" s="2">
+        <v>24</v>
+      </c>
+      <c r="F31" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <v>30000031</v>
+      </c>
+      <c r="B32" s="1">
+        <v>4</v>
+      </c>
+      <c r="C32" s="1">
+        <v>1</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E32" s="1">
+        <v>6</v>
+      </c>
+      <c r="F32" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
+        <v>30000032</v>
+      </c>
+      <c r="B33" s="1">
+        <v>4</v>
+      </c>
+      <c r="C33" s="1">
+        <v>1</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E33" s="1">
+        <v>6</v>
+      </c>
+      <c r="F33" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <v>30000033</v>
+      </c>
+      <c r="B34" s="1">
+        <v>4</v>
+      </c>
+      <c r="C34" s="1">
+        <v>1</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E34" s="1">
+        <v>4</v>
+      </c>
+      <c r="F34" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <v>30000034</v>
+      </c>
+      <c r="B35" s="1">
+        <v>4</v>
+      </c>
+      <c r="C35" s="1">
+        <v>2</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E35" s="1">
+        <v>6</v>
+      </c>
+      <c r="F35" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="1">
+        <v>30000035</v>
+      </c>
+      <c r="B36" s="1">
+        <v>4</v>
+      </c>
+      <c r="C36" s="1">
+        <v>2</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E36" s="1">
+        <v>6</v>
+      </c>
+      <c r="F36" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <v>30000036</v>
+      </c>
+      <c r="B37" s="1">
+        <v>4</v>
+      </c>
+      <c r="C37" s="1">
+        <v>2</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E37" s="1">
+        <v>4</v>
+      </c>
+      <c r="F37" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="1">
+        <v>30000037</v>
+      </c>
+      <c r="B38" s="1">
+        <v>4</v>
+      </c>
+      <c r="C38" s="1">
+        <v>3</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E38" s="1">
+        <v>12</v>
+      </c>
+      <c r="F38" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
+        <v>30000038</v>
+      </c>
+      <c r="B39" s="1">
+        <v>4</v>
+      </c>
+      <c r="C39" s="1">
+        <v>3</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E39" s="1">
+        <v>12</v>
+      </c>
+      <c r="F39" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="1">
+        <v>30000039</v>
+      </c>
+      <c r="B40" s="1">
+        <v>4</v>
+      </c>
+      <c r="C40" s="1">
+        <v>3</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E40" s="1">
+        <v>8</v>
+      </c>
+      <c r="F40" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="1">
+        <v>30000040</v>
+      </c>
+      <c r="B41" s="1">
+        <v>4</v>
+      </c>
+      <c r="C41" s="1">
+        <v>4</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E41" s="1">
+        <v>12</v>
+      </c>
+      <c r="F41" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="1">
+        <v>30000041</v>
+      </c>
+      <c r="B42" s="1">
+        <v>4</v>
+      </c>
+      <c r="C42" s="1">
+        <v>4</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E42" s="1">
+        <v>12</v>
+      </c>
+      <c r="F42" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="1">
+        <v>30000042</v>
+      </c>
+      <c r="B43" s="1">
+        <v>4</v>
+      </c>
+      <c r="C43" s="1">
+        <v>4</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E43" s="1">
+        <v>8</v>
+      </c>
+      <c r="F43" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="1">
+        <v>30000043</v>
+      </c>
+      <c r="B44" s="1">
+        <v>4</v>
+      </c>
+      <c r="C44" s="1">
+        <v>5</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E44" s="1">
+        <v>16</v>
+      </c>
+      <c r="F44" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" s="1">
+        <v>30000044</v>
+      </c>
+      <c r="B45" s="1">
+        <v>4</v>
+      </c>
+      <c r="C45" s="1">
+        <v>5</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E45" s="1">
+        <v>16</v>
+      </c>
+      <c r="F45" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" s="1">
+        <v>30000045</v>
+      </c>
+      <c r="B46" s="1">
+        <v>4</v>
+      </c>
+      <c r="C46" s="1">
+        <v>5</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E46" s="1">
+        <v>12</v>
+      </c>
+      <c r="F46" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" s="2">
+        <v>30000046</v>
+      </c>
+      <c r="B47" s="2">
+        <v>5</v>
+      </c>
+      <c r="C47" s="2">
+        <v>1</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E47" s="2">
+        <v>6</v>
+      </c>
+      <c r="F47" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="2">
+        <v>30000047</v>
+      </c>
+      <c r="B48" s="2">
+        <v>5</v>
+      </c>
+      <c r="C48" s="2">
+        <v>1</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E48" s="2">
+        <v>6</v>
+      </c>
+      <c r="F48" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" s="2">
+        <v>30000048</v>
+      </c>
+      <c r="B49" s="2">
+        <v>5</v>
+      </c>
+      <c r="C49" s="2">
+        <v>1</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E49" s="2">
+        <v>4</v>
+      </c>
+      <c r="F49" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" s="2">
+        <v>30000049</v>
+      </c>
+      <c r="B50" s="2">
+        <v>5</v>
+      </c>
+      <c r="C50" s="2">
+        <v>2</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E50" s="2">
+        <v>6</v>
+      </c>
+      <c r="F50" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" s="2">
+        <v>30000050</v>
+      </c>
+      <c r="B51" s="2">
+        <v>5</v>
+      </c>
+      <c r="C51" s="2">
+        <v>2</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E51" s="2">
+        <v>6</v>
+      </c>
+      <c r="F51" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" s="2">
+        <v>30000051</v>
+      </c>
+      <c r="B52" s="2">
+        <v>5</v>
+      </c>
+      <c r="C52" s="2">
+        <v>2</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E52" s="2">
+        <v>4</v>
+      </c>
+      <c r="F52" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53" s="2">
+        <v>30000052</v>
+      </c>
+      <c r="B53" s="2">
+        <v>5</v>
+      </c>
+      <c r="C53" s="2">
+        <v>3</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E53" s="2">
+        <v>12</v>
+      </c>
+      <c r="F53" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54" s="2">
+        <v>30000053</v>
+      </c>
+      <c r="B54" s="2">
+        <v>5</v>
+      </c>
+      <c r="C54" s="2">
+        <v>3</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E54" s="2">
+        <v>12</v>
+      </c>
+      <c r="F54" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55" s="2">
+        <v>30000054</v>
+      </c>
+      <c r="B55" s="2">
+        <v>5</v>
+      </c>
+      <c r="C55" s="2">
+        <v>3</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E55" s="2">
+        <v>8</v>
+      </c>
+      <c r="F55" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56" s="2">
+        <v>30000055</v>
+      </c>
+      <c r="B56" s="2">
+        <v>5</v>
+      </c>
+      <c r="C56" s="2">
+        <v>4</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E56" s="2">
+        <v>12</v>
+      </c>
+      <c r="F56" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57" s="2">
+        <v>30000056</v>
+      </c>
+      <c r="B57" s="2">
+        <v>5</v>
+      </c>
+      <c r="C57" s="2">
+        <v>4</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E57" s="2">
+        <v>12</v>
+      </c>
+      <c r="F57" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A58" s="2">
+        <v>30000057</v>
+      </c>
+      <c r="B58" s="2">
+        <v>5</v>
+      </c>
+      <c r="C58" s="2">
+        <v>4</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E58" s="2">
+        <v>8</v>
+      </c>
+      <c r="F58" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A59" s="2">
+        <v>30000058</v>
+      </c>
+      <c r="B59" s="2">
+        <v>5</v>
+      </c>
+      <c r="C59" s="2">
+        <v>5</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E59" s="2">
+        <v>16</v>
+      </c>
+      <c r="F59" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60" s="2">
+        <v>30000059</v>
+      </c>
+      <c r="B60" s="2">
+        <v>5</v>
+      </c>
+      <c r="C60" s="2">
+        <v>5</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E60" s="2">
+        <v>16</v>
+      </c>
+      <c r="F60" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A61" s="2">
+        <v>30000060</v>
+      </c>
+      <c r="B61" s="2">
+        <v>5</v>
+      </c>
+      <c r="C61" s="2">
+        <v>5</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E61" s="2">
+        <v>12</v>
+      </c>
+      <c r="F61" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A62" s="1">
+        <v>30000061</v>
+      </c>
+      <c r="B62" s="1">
+        <v>6</v>
+      </c>
+      <c r="C62" s="1">
+        <v>1</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E62" s="1">
+        <v>6</v>
+      </c>
+      <c r="F62" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A63" s="1">
+        <v>30000062</v>
+      </c>
+      <c r="B63" s="1">
+        <v>6</v>
+      </c>
+      <c r="C63" s="1">
+        <v>1</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E63" s="1">
+        <v>6</v>
+      </c>
+      <c r="F63" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A64" s="1">
+        <v>30000063</v>
+      </c>
+      <c r="B64" s="1">
+        <v>6</v>
+      </c>
+      <c r="C64" s="1">
+        <v>1</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E64" s="1">
+        <v>4</v>
+      </c>
+      <c r="F64" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A65" s="1">
+        <v>30000064</v>
+      </c>
+      <c r="B65" s="1">
+        <v>6</v>
+      </c>
+      <c r="C65" s="1">
+        <v>2</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E65" s="1">
+        <v>6</v>
+      </c>
+      <c r="F65" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A66" s="1">
+        <v>30000065</v>
+      </c>
+      <c r="B66" s="1">
+        <v>6</v>
+      </c>
+      <c r="C66" s="1">
+        <v>2</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E66" s="1">
+        <v>6</v>
+      </c>
+      <c r="F66" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A67" s="1">
+        <v>30000066</v>
+      </c>
+      <c r="B67" s="1">
+        <v>6</v>
+      </c>
+      <c r="C67" s="1">
+        <v>2</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E67" s="1">
+        <v>4</v>
+      </c>
+      <c r="F67" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A68" s="1">
+        <v>30000067</v>
+      </c>
+      <c r="B68" s="1">
+        <v>6</v>
+      </c>
+      <c r="C68" s="1">
+        <v>3</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E68" s="1">
+        <v>12</v>
+      </c>
+      <c r="F68" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A69" s="1">
+        <v>30000068</v>
+      </c>
+      <c r="B69" s="1">
+        <v>6</v>
+      </c>
+      <c r="C69" s="1">
+        <v>3</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E69" s="1">
+        <v>12</v>
+      </c>
+      <c r="F69" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A70" s="1">
+        <v>30000069</v>
+      </c>
+      <c r="B70" s="1">
+        <v>6</v>
+      </c>
+      <c r="C70" s="1">
+        <v>3</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E70" s="1">
+        <v>8</v>
+      </c>
+      <c r="F70" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A71" s="1">
+        <v>30000070</v>
+      </c>
+      <c r="B71" s="1">
+        <v>6</v>
+      </c>
+      <c r="C71" s="1">
+        <v>4</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E71" s="1">
+        <v>12</v>
+      </c>
+      <c r="F71" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A72" s="1">
+        <v>30000071</v>
+      </c>
+      <c r="B72" s="1">
+        <v>6</v>
+      </c>
+      <c r="C72" s="1">
+        <v>4</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E72" s="1">
+        <v>12</v>
+      </c>
+      <c r="F72" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A73" s="1">
+        <v>30000072</v>
+      </c>
+      <c r="B73" s="1">
+        <v>6</v>
+      </c>
+      <c r="C73" s="1">
+        <v>4</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E73" s="1">
+        <v>8</v>
+      </c>
+      <c r="F73" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A74" s="1">
+        <v>30000073</v>
+      </c>
+      <c r="B74" s="1">
+        <v>6</v>
+      </c>
+      <c r="C74" s="1">
+        <v>5</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E74" s="1">
+        <v>16</v>
+      </c>
+      <c r="F74" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A75" s="1">
+        <v>30000074</v>
+      </c>
+      <c r="B75" s="1">
+        <v>6</v>
+      </c>
+      <c r="C75" s="1">
+        <v>5</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E75" s="1">
+        <v>16</v>
+      </c>
+      <c r="F75" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A76" s="1">
+        <v>30000075</v>
+      </c>
+      <c r="B76" s="1">
+        <v>6</v>
+      </c>
+      <c r="C76" s="1">
+        <v>5</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E76" s="1">
+        <v>12</v>
+      </c>
+      <c r="F76" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A77" s="2">
+        <v>30000076</v>
+      </c>
+      <c r="B77" s="2">
+        <v>7</v>
+      </c>
+      <c r="C77" s="2">
+        <v>1</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E77" s="2">
+        <v>6</v>
+      </c>
+      <c r="F77" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A78" s="2">
+        <v>30000077</v>
+      </c>
+      <c r="B78" s="2">
+        <v>7</v>
+      </c>
+      <c r="C78" s="2">
+        <v>1</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E78" s="2">
+        <v>6</v>
+      </c>
+      <c r="F78" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A79" s="2">
+        <v>30000078</v>
+      </c>
+      <c r="B79" s="2">
+        <v>7</v>
+      </c>
+      <c r="C79" s="2">
+        <v>1</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E79" s="2">
+        <v>2</v>
+      </c>
+      <c r="F79" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A80" s="2">
+        <v>30000079</v>
+      </c>
+      <c r="B80" s="2">
+        <v>7</v>
+      </c>
+      <c r="C80" s="2">
+        <v>1</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E80" s="2">
+        <v>2</v>
+      </c>
+      <c r="F80" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A81" s="2">
+        <v>30000080</v>
+      </c>
+      <c r="B81" s="2">
+        <v>7</v>
+      </c>
+      <c r="C81" s="2">
+        <v>2</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E81" s="2">
+        <v>6</v>
+      </c>
+      <c r="F81" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A82" s="2">
+        <v>30000081</v>
+      </c>
+      <c r="B82" s="2">
+        <v>7</v>
+      </c>
+      <c r="C82" s="2">
+        <v>2</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E82" s="2">
+        <v>6</v>
+      </c>
+      <c r="F82" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A83" s="2">
+        <v>30000082</v>
+      </c>
+      <c r="B83" s="2">
+        <v>7</v>
+      </c>
+      <c r="C83" s="2">
+        <v>2</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E83" s="2">
+        <v>2</v>
+      </c>
+      <c r="F83" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A84" s="2">
+        <v>30000083</v>
+      </c>
+      <c r="B84" s="2">
+        <v>7</v>
+      </c>
+      <c r="C84" s="2">
+        <v>2</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E84" s="2">
+        <v>2</v>
+      </c>
+      <c r="F84" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A85" s="2">
+        <v>30000084</v>
+      </c>
+      <c r="B85" s="2">
+        <v>7</v>
+      </c>
+      <c r="C85" s="2">
+        <v>3</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E85" s="2">
+        <v>12</v>
+      </c>
+      <c r="F85" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A86" s="2">
+        <v>30000085</v>
+      </c>
+      <c r="B86" s="2">
+        <v>7</v>
+      </c>
+      <c r="C86" s="2">
+        <v>3</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E86" s="2">
+        <v>12</v>
+      </c>
+      <c r="F86" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A87" s="2">
+        <v>30000086</v>
+      </c>
+      <c r="B87" s="2">
+        <v>7</v>
+      </c>
+      <c r="C87" s="2">
+        <v>3</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E87" s="2">
+        <v>4</v>
+      </c>
+      <c r="F87" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A88" s="2">
+        <v>30000087</v>
+      </c>
+      <c r="B88" s="2">
+        <v>7</v>
+      </c>
+      <c r="C88" s="2">
+        <v>3</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E88" s="2">
+        <v>4</v>
+      </c>
+      <c r="F88" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A89" s="2">
+        <v>30000088</v>
+      </c>
+      <c r="B89" s="2">
+        <v>7</v>
+      </c>
+      <c r="C89" s="2">
+        <v>4</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E89" s="2">
+        <v>12</v>
+      </c>
+      <c r="F89" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A90" s="2">
+        <v>30000089</v>
+      </c>
+      <c r="B90" s="2">
+        <v>7</v>
+      </c>
+      <c r="C90" s="2">
+        <v>4</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E90" s="2">
+        <v>12</v>
+      </c>
+      <c r="F90" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A91" s="2">
+        <v>30000090</v>
+      </c>
+      <c r="B91" s="2">
+        <v>7</v>
+      </c>
+      <c r="C91" s="2">
+        <v>4</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E91" s="2">
+        <v>4</v>
+      </c>
+      <c r="F91" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A92" s="2">
+        <v>30000091</v>
+      </c>
+      <c r="B92" s="2">
+        <v>7</v>
+      </c>
+      <c r="C92" s="2">
+        <v>4</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E92" s="2">
+        <v>4</v>
+      </c>
+      <c r="F92" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A93" s="2">
+        <v>30000092</v>
+      </c>
+      <c r="B93" s="2">
+        <v>7</v>
+      </c>
+      <c r="C93" s="2">
+        <v>5</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E93" s="2">
+        <v>16</v>
+      </c>
+      <c r="F93" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A94" s="2">
+        <v>30000093</v>
+      </c>
+      <c r="B94" s="2">
+        <v>7</v>
+      </c>
+      <c r="C94" s="2">
+        <v>5</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E94" s="2">
+        <v>16</v>
+      </c>
+      <c r="F94" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A95" s="2">
+        <v>30000094</v>
+      </c>
+      <c r="B95" s="2">
+        <v>7</v>
+      </c>
+      <c r="C95" s="2">
+        <v>5</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E95" s="2">
+        <v>8</v>
+      </c>
+      <c r="F95" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A96" s="2">
+        <v>30000095</v>
+      </c>
+      <c r="B96" s="2">
+        <v>7</v>
+      </c>
+      <c r="C96" s="2">
+        <v>5</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E96" s="2">
+        <v>8</v>
+      </c>
+      <c r="F96" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A97" s="1">
+        <v>30000096</v>
+      </c>
+      <c r="B97" s="1">
+        <v>8</v>
+      </c>
+      <c r="C97" s="1">
+        <v>1</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E97" s="1">
+        <v>6</v>
+      </c>
+      <c r="F97" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A98" s="1">
+        <v>30000097</v>
+      </c>
+      <c r="B98" s="1">
+        <v>8</v>
+      </c>
+      <c r="C98" s="1">
+        <v>1</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E98" s="1">
+        <v>6</v>
+      </c>
+      <c r="F98" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A99" s="1">
+        <v>30000098</v>
+      </c>
+      <c r="B99" s="1">
+        <v>8</v>
+      </c>
+      <c r="C99" s="1">
+        <v>1</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E99" s="1">
+        <v>2</v>
+      </c>
+      <c r="F99" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A100" s="1">
+        <v>30000099</v>
+      </c>
+      <c r="B100" s="1">
+        <v>8</v>
+      </c>
+      <c r="C100" s="1">
+        <v>1</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E100" s="1">
+        <v>2</v>
+      </c>
+      <c r="F100" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A101" s="1">
+        <v>30000100</v>
+      </c>
+      <c r="B101" s="1">
+        <v>8</v>
+      </c>
+      <c r="C101" s="1">
+        <v>2</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E101" s="1">
+        <v>6</v>
+      </c>
+      <c r="F101" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A102" s="1">
+        <v>30000101</v>
+      </c>
+      <c r="B102" s="1">
+        <v>8</v>
+      </c>
+      <c r="C102" s="1">
+        <v>2</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E102" s="1">
+        <v>6</v>
+      </c>
+      <c r="F102" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A103" s="1">
+        <v>30000102</v>
+      </c>
+      <c r="B103" s="1">
+        <v>8</v>
+      </c>
+      <c r="C103" s="1">
+        <v>2</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E103" s="1">
+        <v>2</v>
+      </c>
+      <c r="F103" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A104" s="1">
+        <v>30000103</v>
+      </c>
+      <c r="B104" s="1">
+        <v>8</v>
+      </c>
+      <c r="C104" s="1">
+        <v>2</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E104" s="1">
+        <v>2</v>
+      </c>
+      <c r="F104" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A105" s="1">
+        <v>30000104</v>
+      </c>
+      <c r="B105" s="1">
+        <v>8</v>
+      </c>
+      <c r="C105" s="1">
+        <v>3</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E105" s="1">
+        <v>12</v>
+      </c>
+      <c r="F105" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A106" s="1">
+        <v>30000105</v>
+      </c>
+      <c r="B106" s="1">
+        <v>8</v>
+      </c>
+      <c r="C106" s="1">
+        <v>3</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E106" s="1">
+        <v>12</v>
+      </c>
+      <c r="F106" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A107" s="1">
+        <v>30000106</v>
+      </c>
+      <c r="B107" s="1">
+        <v>8</v>
+      </c>
+      <c r="C107" s="1">
+        <v>3</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E107" s="1">
+        <v>4</v>
+      </c>
+      <c r="F107" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A108" s="1">
+        <v>30000107</v>
+      </c>
+      <c r="B108" s="1">
+        <v>8</v>
+      </c>
+      <c r="C108" s="1">
+        <v>3</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E108" s="1">
+        <v>4</v>
+      </c>
+      <c r="F108" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A109" s="1">
+        <v>30000108</v>
+      </c>
+      <c r="B109" s="1">
+        <v>8</v>
+      </c>
+      <c r="C109" s="1">
+        <v>4</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E109" s="1">
+        <v>12</v>
+      </c>
+      <c r="F109" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A110" s="1">
+        <v>30000109</v>
+      </c>
+      <c r="B110" s="1">
+        <v>8</v>
+      </c>
+      <c r="C110" s="1">
+        <v>4</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E110" s="1">
+        <v>12</v>
+      </c>
+      <c r="F110" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A111" s="1">
+        <v>30000110</v>
+      </c>
+      <c r="B111" s="1">
+        <v>8</v>
+      </c>
+      <c r="C111" s="1">
+        <v>4</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E111" s="1">
+        <v>4</v>
+      </c>
+      <c r="F111" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A112" s="1">
+        <v>30000111</v>
+      </c>
+      <c r="B112" s="1">
+        <v>8</v>
+      </c>
+      <c r="C112" s="1">
+        <v>4</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E112" s="1">
+        <v>4</v>
+      </c>
+      <c r="F112" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A113" s="1">
+        <v>30000112</v>
+      </c>
+      <c r="B113" s="1">
+        <v>8</v>
+      </c>
+      <c r="C113" s="1">
+        <v>5</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E113" s="1">
+        <v>16</v>
+      </c>
+      <c r="F113" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A114" s="1">
+        <v>30000113</v>
+      </c>
+      <c r="B114" s="1">
+        <v>8</v>
+      </c>
+      <c r="C114" s="1">
+        <v>5</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E114" s="1">
+        <v>16</v>
+      </c>
+      <c r="F114" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A115" s="1">
+        <v>30000114</v>
+      </c>
+      <c r="B115" s="1">
+        <v>8</v>
+      </c>
+      <c r="C115" s="1">
+        <v>5</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E115" s="1">
+        <v>8</v>
+      </c>
+      <c r="F115" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A116" s="1">
+        <v>30000115</v>
+      </c>
+      <c r="B116" s="1">
+        <v>8</v>
+      </c>
+      <c r="C116" s="1">
+        <v>5</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E116" s="1">
+        <v>8</v>
+      </c>
+      <c r="F116" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A117" s="2">
+        <v>30000116</v>
+      </c>
+      <c r="B117" s="2">
+        <v>9</v>
+      </c>
+      <c r="C117" s="2">
+        <v>1</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E117" s="2">
+        <v>6</v>
+      </c>
+      <c r="F117" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A118" s="2">
+        <v>20000117</v>
+      </c>
+      <c r="B118" s="2">
+        <v>9</v>
+      </c>
+      <c r="C118" s="2">
+        <v>1</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E118" s="2">
+        <v>6</v>
+      </c>
+      <c r="F118" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A119" s="2">
+        <v>20000118</v>
+      </c>
+      <c r="B119" s="2">
+        <v>9</v>
+      </c>
+      <c r="C119" s="2">
+        <v>1</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E119" s="2">
+        <v>2</v>
+      </c>
+      <c r="F119" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A120" s="2">
+        <v>20000119</v>
+      </c>
+      <c r="B120" s="2">
+        <v>9</v>
+      </c>
+      <c r="C120" s="2">
+        <v>1</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E120" s="2">
+        <v>2</v>
+      </c>
+      <c r="F120" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A121" s="2">
+        <v>20000120</v>
+      </c>
+      <c r="B121" s="2">
+        <v>9</v>
+      </c>
+      <c r="C121" s="2">
+        <v>2</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E121" s="2">
+        <v>6</v>
+      </c>
+      <c r="F121" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A122" s="2">
+        <v>20000121</v>
+      </c>
+      <c r="B122" s="2">
+        <v>9</v>
+      </c>
+      <c r="C122" s="2">
+        <v>2</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E122" s="2">
+        <v>6</v>
+      </c>
+      <c r="F122" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A123" s="2">
+        <v>20000122</v>
+      </c>
+      <c r="B123" s="2">
+        <v>9</v>
+      </c>
+      <c r="C123" s="2">
+        <v>2</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E123" s="2">
+        <v>2</v>
+      </c>
+      <c r="F123" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A124" s="2">
+        <v>20000123</v>
+      </c>
+      <c r="B124" s="2">
+        <v>9</v>
+      </c>
+      <c r="C124" s="2">
+        <v>2</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E124" s="2">
+        <v>2</v>
+      </c>
+      <c r="F124" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A125" s="2">
+        <v>20000124</v>
+      </c>
+      <c r="B125" s="2">
+        <v>9</v>
+      </c>
+      <c r="C125" s="2">
+        <v>3</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E125" s="2">
+        <v>12</v>
+      </c>
+      <c r="F125" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A126" s="2">
+        <v>20000125</v>
+      </c>
+      <c r="B126" s="2">
+        <v>9</v>
+      </c>
+      <c r="C126" s="2">
+        <v>3</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E126" s="2">
+        <v>12</v>
+      </c>
+      <c r="F126" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A127" s="2">
+        <v>20000126</v>
+      </c>
+      <c r="B127" s="2">
+        <v>9</v>
+      </c>
+      <c r="C127" s="2">
+        <v>3</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E127" s="2">
+        <v>4</v>
+      </c>
+      <c r="F127" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A128" s="2">
+        <v>20000127</v>
+      </c>
+      <c r="B128" s="2">
+        <v>9</v>
+      </c>
+      <c r="C128" s="2">
+        <v>3</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E128" s="2">
+        <v>4</v>
+      </c>
+      <c r="F128" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A129" s="2">
+        <v>20000128</v>
+      </c>
+      <c r="B129" s="2">
+        <v>9</v>
+      </c>
+      <c r="C129" s="2">
+        <v>4</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E129" s="2">
+        <v>12</v>
+      </c>
+      <c r="F129" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A130" s="2">
+        <v>20000129</v>
+      </c>
+      <c r="B130" s="2">
+        <v>9</v>
+      </c>
+      <c r="C130" s="2">
+        <v>4</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E130" s="2">
+        <v>12</v>
+      </c>
+      <c r="F130" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A131" s="2">
+        <v>20000130</v>
+      </c>
+      <c r="B131" s="2">
+        <v>9</v>
+      </c>
+      <c r="C131" s="2">
+        <v>4</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E131" s="2">
+        <v>4</v>
+      </c>
+      <c r="F131" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A132" s="2">
+        <v>20000131</v>
+      </c>
+      <c r="B132" s="2">
+        <v>9</v>
+      </c>
+      <c r="C132" s="2">
+        <v>4</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E132" s="2">
+        <v>4</v>
+      </c>
+      <c r="F132" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A133" s="2">
+        <v>20000132</v>
+      </c>
+      <c r="B133" s="2">
+        <v>9</v>
+      </c>
+      <c r="C133" s="2">
+        <v>5</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E133" s="2">
+        <v>16</v>
+      </c>
+      <c r="F133" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A134" s="2">
+        <v>20000133</v>
+      </c>
+      <c r="B134" s="2">
+        <v>9</v>
+      </c>
+      <c r="C134" s="2">
+        <v>5</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E134" s="2">
+        <v>16</v>
+      </c>
+      <c r="F134" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A135" s="2">
+        <v>20000134</v>
+      </c>
+      <c r="B135" s="2">
+        <v>9</v>
+      </c>
+      <c r="C135" s="2">
+        <v>5</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E135" s="2">
+        <v>8</v>
+      </c>
+      <c r="F135" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A136" s="2">
+        <v>30000116</v>
+      </c>
+      <c r="B136" s="2">
+        <v>9</v>
+      </c>
+      <c r="C136" s="2">
+        <v>5</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E136" s="2">
+        <v>8</v>
+      </c>
+      <c r="F136" s="2">
+        <v>120</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F871538F-A8B6-4F35-AFAA-22D40658E79C}">
+  <dimension ref="A1:F136"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>40000001</v>
+      </c>
+      <c r="B2" s="2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="2">
+        <v>8</v>
+      </c>
+      <c r="F2" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>40000002</v>
+      </c>
+      <c r="B3" s="2">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="2">
+        <v>8</v>
+      </c>
+      <c r="F3" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>40000003</v>
+      </c>
+      <c r="B4" s="2">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2">
+        <v>2</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="2">
+        <v>8</v>
+      </c>
+      <c r="F4" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>40000004</v>
+      </c>
+      <c r="B5" s="2">
+        <v>1</v>
+      </c>
+      <c r="C5" s="2">
+        <v>2</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="2">
+        <v>8</v>
+      </c>
+      <c r="F5" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>40000005</v>
+      </c>
+      <c r="B6" s="2">
+        <v>1</v>
+      </c>
+      <c r="C6" s="2">
+        <v>3</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="2">
+        <v>16</v>
+      </c>
+      <c r="F6" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>40000006</v>
+      </c>
+      <c r="B7" s="2">
+        <v>1</v>
+      </c>
+      <c r="C7" s="2">
+        <v>3</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="2">
+        <v>16</v>
+      </c>
+      <c r="F7" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>40000007</v>
+      </c>
+      <c r="B8" s="2">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2">
+        <v>4</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="2">
+        <v>16</v>
+      </c>
+      <c r="F8" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>40000008</v>
+      </c>
+      <c r="B9" s="2">
+        <v>1</v>
+      </c>
+      <c r="C9" s="2">
+        <v>4</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="2">
+        <v>16</v>
+      </c>
+      <c r="F9" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>40000009</v>
+      </c>
+      <c r="B10" s="2">
+        <v>1</v>
+      </c>
+      <c r="C10" s="2">
+        <v>5</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="2">
+        <v>24</v>
+      </c>
+      <c r="F10" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>40000010</v>
+      </c>
+      <c r="B11" s="2">
+        <v>1</v>
+      </c>
+      <c r="C11" s="2">
+        <v>5</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" s="2">
+        <v>24</v>
+      </c>
+      <c r="F11" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>40000011</v>
+      </c>
+      <c r="B12" s="1">
+        <v>2</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="1">
+        <v>8</v>
+      </c>
+      <c r="F12" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>40000012</v>
+      </c>
+      <c r="B13" s="1">
+        <v>2</v>
+      </c>
+      <c r="C13" s="1">
+        <v>1</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" s="1">
+        <v>8</v>
+      </c>
+      <c r="F13" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <v>40000013</v>
+      </c>
+      <c r="B14" s="1">
+        <v>2</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14" s="1">
+        <v>8</v>
+      </c>
+      <c r="F14" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>40000014</v>
+      </c>
+      <c r="B15" s="1">
+        <v>2</v>
+      </c>
+      <c r="C15" s="1">
+        <v>2</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="1">
+        <v>8</v>
+      </c>
+      <c r="F15" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>40000015</v>
+      </c>
+      <c r="B16" s="1">
+        <v>2</v>
+      </c>
+      <c r="C16" s="1">
+        <v>3</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" s="1">
+        <v>16</v>
+      </c>
+      <c r="F16" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>40000016</v>
+      </c>
+      <c r="B17" s="1">
+        <v>2</v>
+      </c>
+      <c r="C17" s="1">
+        <v>3</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" s="1">
+        <v>16</v>
+      </c>
+      <c r="F17" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>40000017</v>
+      </c>
+      <c r="B18" s="1">
+        <v>2</v>
+      </c>
+      <c r="C18" s="1">
+        <v>4</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18" s="1">
+        <v>16</v>
+      </c>
+      <c r="F18" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <v>40000018</v>
+      </c>
+      <c r="B19" s="1">
+        <v>2</v>
+      </c>
+      <c r="C19" s="1">
+        <v>4</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" s="1">
+        <v>16</v>
+      </c>
+      <c r="F19" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <v>40000019</v>
+      </c>
+      <c r="B20" s="1">
+        <v>2</v>
+      </c>
+      <c r="C20" s="1">
+        <v>5</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E20" s="1">
+        <v>24</v>
+      </c>
+      <c r="F20" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <v>40000020</v>
+      </c>
+      <c r="B21" s="1">
+        <v>2</v>
+      </c>
+      <c r="C21" s="1">
+        <v>5</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E21" s="1">
+        <v>24</v>
+      </c>
+      <c r="F21" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="2">
+        <v>40000021</v>
+      </c>
+      <c r="B22" s="2">
+        <v>3</v>
+      </c>
+      <c r="C22" s="2">
+        <v>1</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E22" s="2">
+        <v>8</v>
+      </c>
+      <c r="F22" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="2">
+        <v>40000022</v>
+      </c>
+      <c r="B23" s="2">
+        <v>3</v>
+      </c>
+      <c r="C23" s="2">
+        <v>1</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E23" s="2">
+        <v>8</v>
+      </c>
+      <c r="F23" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="2">
+        <v>40000023</v>
+      </c>
+      <c r="B24" s="2">
+        <v>3</v>
+      </c>
+      <c r="C24" s="2">
+        <v>2</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E24" s="2">
+        <v>8</v>
+      </c>
+      <c r="F24" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="2">
+        <v>40000024</v>
+      </c>
+      <c r="B25" s="2">
+        <v>3</v>
+      </c>
+      <c r="C25" s="2">
+        <v>2</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E25" s="2">
+        <v>8</v>
+      </c>
+      <c r="F25" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="2">
+        <v>40000025</v>
+      </c>
+      <c r="B26" s="2">
+        <v>3</v>
+      </c>
+      <c r="C26" s="2">
+        <v>3</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E26" s="2">
+        <v>16</v>
+      </c>
+      <c r="F26" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="2">
+        <v>40000026</v>
+      </c>
+      <c r="B27" s="2">
+        <v>3</v>
+      </c>
+      <c r="C27" s="2">
+        <v>3</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E27" s="2">
+        <v>16</v>
+      </c>
+      <c r="F27" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="2">
+        <v>40000027</v>
+      </c>
+      <c r="B28" s="2">
+        <v>3</v>
+      </c>
+      <c r="C28" s="2">
+        <v>4</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E28" s="2">
+        <v>16</v>
+      </c>
+      <c r="F28" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="2">
+        <v>40000028</v>
+      </c>
+      <c r="B29" s="2">
+        <v>3</v>
+      </c>
+      <c r="C29" s="2">
+        <v>4</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E29" s="2">
+        <v>16</v>
+      </c>
+      <c r="F29" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="2">
+        <v>40000029</v>
+      </c>
+      <c r="B30" s="2">
+        <v>3</v>
+      </c>
+      <c r="C30" s="2">
+        <v>5</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E30" s="2">
+        <v>24</v>
+      </c>
+      <c r="F30" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="2">
+        <v>40000030</v>
+      </c>
+      <c r="B31" s="2">
+        <v>3</v>
+      </c>
+      <c r="C31" s="2">
+        <v>5</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E31" s="2">
+        <v>24</v>
+      </c>
+      <c r="F31" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <v>40000031</v>
+      </c>
+      <c r="B32" s="1">
+        <v>4</v>
+      </c>
+      <c r="C32" s="1">
+        <v>1</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E32" s="1">
+        <v>6</v>
+      </c>
+      <c r="F32" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
+        <v>40000032</v>
+      </c>
+      <c r="B33" s="1">
+        <v>4</v>
+      </c>
+      <c r="C33" s="1">
+        <v>1</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E33" s="1">
+        <v>6</v>
+      </c>
+      <c r="F33" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <v>40000033</v>
+      </c>
+      <c r="B34" s="1">
+        <v>4</v>
+      </c>
+      <c r="C34" s="1">
+        <v>1</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E34" s="1">
+        <v>4</v>
+      </c>
+      <c r="F34" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <v>40000034</v>
+      </c>
+      <c r="B35" s="1">
+        <v>4</v>
+      </c>
+      <c r="C35" s="1">
+        <v>2</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E35" s="1">
+        <v>6</v>
+      </c>
+      <c r="F35" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="1">
+        <v>40000035</v>
+      </c>
+      <c r="B36" s="1">
+        <v>4</v>
+      </c>
+      <c r="C36" s="1">
+        <v>2</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E36" s="1">
+        <v>6</v>
+      </c>
+      <c r="F36" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <v>40000036</v>
+      </c>
+      <c r="B37" s="1">
+        <v>4</v>
+      </c>
+      <c r="C37" s="1">
+        <v>2</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E37" s="1">
+        <v>4</v>
+      </c>
+      <c r="F37" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="1">
+        <v>40000037</v>
+      </c>
+      <c r="B38" s="1">
+        <v>4</v>
+      </c>
+      <c r="C38" s="1">
+        <v>3</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E38" s="1">
+        <v>12</v>
+      </c>
+      <c r="F38" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
+        <v>40000038</v>
+      </c>
+      <c r="B39" s="1">
+        <v>4</v>
+      </c>
+      <c r="C39" s="1">
+        <v>3</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E39" s="1">
+        <v>12</v>
+      </c>
+      <c r="F39" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="1">
+        <v>40000039</v>
+      </c>
+      <c r="B40" s="1">
+        <v>4</v>
+      </c>
+      <c r="C40" s="1">
+        <v>3</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E40" s="1">
+        <v>8</v>
+      </c>
+      <c r="F40" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="1">
+        <v>40000040</v>
+      </c>
+      <c r="B41" s="1">
+        <v>4</v>
+      </c>
+      <c r="C41" s="1">
+        <v>4</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E41" s="1">
+        <v>12</v>
+      </c>
+      <c r="F41" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="1">
+        <v>40000041</v>
+      </c>
+      <c r="B42" s="1">
+        <v>4</v>
+      </c>
+      <c r="C42" s="1">
+        <v>4</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E42" s="1">
+        <v>12</v>
+      </c>
+      <c r="F42" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="1">
+        <v>40000042</v>
+      </c>
+      <c r="B43" s="1">
+        <v>4</v>
+      </c>
+      <c r="C43" s="1">
+        <v>4</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E43" s="1">
+        <v>8</v>
+      </c>
+      <c r="F43" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="1">
+        <v>40000043</v>
+      </c>
+      <c r="B44" s="1">
+        <v>4</v>
+      </c>
+      <c r="C44" s="1">
+        <v>5</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E44" s="1">
+        <v>16</v>
+      </c>
+      <c r="F44" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" s="1">
+        <v>40000044</v>
+      </c>
+      <c r="B45" s="1">
+        <v>4</v>
+      </c>
+      <c r="C45" s="1">
+        <v>5</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E45" s="1">
+        <v>16</v>
+      </c>
+      <c r="F45" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" s="1">
+        <v>40000045</v>
+      </c>
+      <c r="B46" s="1">
+        <v>4</v>
+      </c>
+      <c r="C46" s="1">
+        <v>5</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E46" s="1">
+        <v>12</v>
+      </c>
+      <c r="F46" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" s="2">
+        <v>40000046</v>
+      </c>
+      <c r="B47" s="2">
+        <v>5</v>
+      </c>
+      <c r="C47" s="2">
+        <v>1</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E47" s="2">
+        <v>6</v>
+      </c>
+      <c r="F47" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="2">
+        <v>40000047</v>
+      </c>
+      <c r="B48" s="2">
+        <v>5</v>
+      </c>
+      <c r="C48" s="2">
+        <v>1</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E48" s="2">
+        <v>6</v>
+      </c>
+      <c r="F48" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" s="2">
+        <v>40000048</v>
+      </c>
+      <c r="B49" s="2">
+        <v>5</v>
+      </c>
+      <c r="C49" s="2">
+        <v>1</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E49" s="2">
+        <v>4</v>
+      </c>
+      <c r="F49" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" s="2">
+        <v>40000049</v>
+      </c>
+      <c r="B50" s="2">
+        <v>5</v>
+      </c>
+      <c r="C50" s="2">
+        <v>2</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E50" s="2">
+        <v>6</v>
+      </c>
+      <c r="F50" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" s="2">
+        <v>40000050</v>
+      </c>
+      <c r="B51" s="2">
+        <v>5</v>
+      </c>
+      <c r="C51" s="2">
+        <v>2</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E51" s="2">
+        <v>6</v>
+      </c>
+      <c r="F51" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" s="2">
+        <v>40000051</v>
+      </c>
+      <c r="B52" s="2">
+        <v>5</v>
+      </c>
+      <c r="C52" s="2">
+        <v>2</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E52" s="2">
+        <v>4</v>
+      </c>
+      <c r="F52" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53" s="2">
+        <v>40000052</v>
+      </c>
+      <c r="B53" s="2">
+        <v>5</v>
+      </c>
+      <c r="C53" s="2">
+        <v>3</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E53" s="2">
+        <v>12</v>
+      </c>
+      <c r="F53" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54" s="2">
+        <v>40000053</v>
+      </c>
+      <c r="B54" s="2">
+        <v>5</v>
+      </c>
+      <c r="C54" s="2">
+        <v>3</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E54" s="2">
+        <v>12</v>
+      </c>
+      <c r="F54" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55" s="2">
+        <v>40000054</v>
+      </c>
+      <c r="B55" s="2">
+        <v>5</v>
+      </c>
+      <c r="C55" s="2">
+        <v>3</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E55" s="2">
+        <v>8</v>
+      </c>
+      <c r="F55" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56" s="2">
+        <v>40000055</v>
+      </c>
+      <c r="B56" s="2">
+        <v>5</v>
+      </c>
+      <c r="C56" s="2">
+        <v>4</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E56" s="2">
+        <v>12</v>
+      </c>
+      <c r="F56" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57" s="2">
+        <v>40000056</v>
+      </c>
+      <c r="B57" s="2">
+        <v>5</v>
+      </c>
+      <c r="C57" s="2">
+        <v>4</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E57" s="2">
+        <v>12</v>
+      </c>
+      <c r="F57" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A58" s="2">
+        <v>40000057</v>
+      </c>
+      <c r="B58" s="2">
+        <v>5</v>
+      </c>
+      <c r="C58" s="2">
+        <v>4</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E58" s="2">
+        <v>8</v>
+      </c>
+      <c r="F58" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A59" s="2">
+        <v>40000058</v>
+      </c>
+      <c r="B59" s="2">
+        <v>5</v>
+      </c>
+      <c r="C59" s="2">
+        <v>5</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E59" s="2">
+        <v>16</v>
+      </c>
+      <c r="F59" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60" s="2">
+        <v>40000059</v>
+      </c>
+      <c r="B60" s="2">
+        <v>5</v>
+      </c>
+      <c r="C60" s="2">
+        <v>5</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E60" s="2">
+        <v>16</v>
+      </c>
+      <c r="F60" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A61" s="2">
+        <v>40000060</v>
+      </c>
+      <c r="B61" s="2">
+        <v>5</v>
+      </c>
+      <c r="C61" s="2">
+        <v>5</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E61" s="2">
+        <v>12</v>
+      </c>
+      <c r="F61" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A62" s="1">
+        <v>40000061</v>
+      </c>
+      <c r="B62" s="1">
+        <v>6</v>
+      </c>
+      <c r="C62" s="1">
+        <v>1</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E62" s="1">
+        <v>6</v>
+      </c>
+      <c r="F62" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A63" s="1">
+        <v>40000062</v>
+      </c>
+      <c r="B63" s="1">
+        <v>6</v>
+      </c>
+      <c r="C63" s="1">
+        <v>1</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E63" s="1">
+        <v>6</v>
+      </c>
+      <c r="F63" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A64" s="1">
+        <v>40000063</v>
+      </c>
+      <c r="B64" s="1">
+        <v>6</v>
+      </c>
+      <c r="C64" s="1">
+        <v>1</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E64" s="1">
+        <v>4</v>
+      </c>
+      <c r="F64" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A65" s="1">
+        <v>40000064</v>
+      </c>
+      <c r="B65" s="1">
+        <v>6</v>
+      </c>
+      <c r="C65" s="1">
+        <v>2</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E65" s="1">
+        <v>6</v>
+      </c>
+      <c r="F65" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A66" s="1">
+        <v>40000065</v>
+      </c>
+      <c r="B66" s="1">
+        <v>6</v>
+      </c>
+      <c r="C66" s="1">
+        <v>2</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E66" s="1">
+        <v>6</v>
+      </c>
+      <c r="F66" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A67" s="1">
+        <v>40000066</v>
+      </c>
+      <c r="B67" s="1">
+        <v>6</v>
+      </c>
+      <c r="C67" s="1">
+        <v>2</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E67" s="1">
+        <v>4</v>
+      </c>
+      <c r="F67" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A68" s="1">
+        <v>40000067</v>
+      </c>
+      <c r="B68" s="1">
+        <v>6</v>
+      </c>
+      <c r="C68" s="1">
+        <v>3</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E68" s="1">
+        <v>12</v>
+      </c>
+      <c r="F68" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A69" s="1">
+        <v>40000068</v>
+      </c>
+      <c r="B69" s="1">
+        <v>6</v>
+      </c>
+      <c r="C69" s="1">
+        <v>3</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E69" s="1">
+        <v>12</v>
+      </c>
+      <c r="F69" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A70" s="1">
+        <v>40000069</v>
+      </c>
+      <c r="B70" s="1">
+        <v>6</v>
+      </c>
+      <c r="C70" s="1">
+        <v>3</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E70" s="1">
+        <v>8</v>
+      </c>
+      <c r="F70" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A71" s="1">
+        <v>40000070</v>
+      </c>
+      <c r="B71" s="1">
+        <v>6</v>
+      </c>
+      <c r="C71" s="1">
+        <v>4</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E71" s="1">
+        <v>12</v>
+      </c>
+      <c r="F71" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A72" s="1">
+        <v>40000071</v>
+      </c>
+      <c r="B72" s="1">
+        <v>6</v>
+      </c>
+      <c r="C72" s="1">
+        <v>4</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E72" s="1">
+        <v>12</v>
+      </c>
+      <c r="F72" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A73" s="1">
+        <v>40000072</v>
+      </c>
+      <c r="B73" s="1">
+        <v>6</v>
+      </c>
+      <c r="C73" s="1">
+        <v>4</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E73" s="1">
+        <v>8</v>
+      </c>
+      <c r="F73" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A74" s="1">
+        <v>40000073</v>
+      </c>
+      <c r="B74" s="1">
+        <v>6</v>
+      </c>
+      <c r="C74" s="1">
+        <v>5</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E74" s="1">
+        <v>16</v>
+      </c>
+      <c r="F74" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A75" s="1">
+        <v>40000074</v>
+      </c>
+      <c r="B75" s="1">
+        <v>6</v>
+      </c>
+      <c r="C75" s="1">
+        <v>5</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E75" s="1">
+        <v>16</v>
+      </c>
+      <c r="F75" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A76" s="1">
+        <v>40000075</v>
+      </c>
+      <c r="B76" s="1">
+        <v>6</v>
+      </c>
+      <c r="C76" s="1">
+        <v>5</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E76" s="1">
+        <v>12</v>
+      </c>
+      <c r="F76" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A77" s="2">
+        <v>40000076</v>
+      </c>
+      <c r="B77" s="2">
+        <v>7</v>
+      </c>
+      <c r="C77" s="2">
+        <v>1</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E77" s="2">
+        <v>6</v>
+      </c>
+      <c r="F77" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A78" s="2">
+        <v>40000077</v>
+      </c>
+      <c r="B78" s="2">
+        <v>7</v>
+      </c>
+      <c r="C78" s="2">
+        <v>1</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E78" s="2">
+        <v>6</v>
+      </c>
+      <c r="F78" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A79" s="2">
+        <v>40000078</v>
+      </c>
+      <c r="B79" s="2">
+        <v>7</v>
+      </c>
+      <c r="C79" s="2">
+        <v>1</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E79" s="2">
+        <v>2</v>
+      </c>
+      <c r="F79" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A80" s="2">
+        <v>40000079</v>
+      </c>
+      <c r="B80" s="2">
+        <v>7</v>
+      </c>
+      <c r="C80" s="2">
+        <v>1</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E80" s="2">
+        <v>2</v>
+      </c>
+      <c r="F80" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A81" s="2">
+        <v>40000080</v>
+      </c>
+      <c r="B81" s="2">
+        <v>7</v>
+      </c>
+      <c r="C81" s="2">
+        <v>2</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E81" s="2">
+        <v>6</v>
+      </c>
+      <c r="F81" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A82" s="2">
+        <v>40000081</v>
+      </c>
+      <c r="B82" s="2">
+        <v>7</v>
+      </c>
+      <c r="C82" s="2">
+        <v>2</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E82" s="2">
+        <v>6</v>
+      </c>
+      <c r="F82" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A83" s="2">
+        <v>40000082</v>
+      </c>
+      <c r="B83" s="2">
+        <v>7</v>
+      </c>
+      <c r="C83" s="2">
+        <v>2</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E83" s="2">
+        <v>2</v>
+      </c>
+      <c r="F83" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A84" s="2">
+        <v>40000083</v>
+      </c>
+      <c r="B84" s="2">
+        <v>7</v>
+      </c>
+      <c r="C84" s="2">
+        <v>2</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E84" s="2">
+        <v>2</v>
+      </c>
+      <c r="F84" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A85" s="2">
+        <v>40000084</v>
+      </c>
+      <c r="B85" s="2">
+        <v>7</v>
+      </c>
+      <c r="C85" s="2">
+        <v>3</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E85" s="2">
+        <v>12</v>
+      </c>
+      <c r="F85" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A86" s="2">
+        <v>40000085</v>
+      </c>
+      <c r="B86" s="2">
+        <v>7</v>
+      </c>
+      <c r="C86" s="2">
+        <v>3</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E86" s="2">
+        <v>12</v>
+      </c>
+      <c r="F86" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A87" s="2">
+        <v>40000086</v>
+      </c>
+      <c r="B87" s="2">
+        <v>7</v>
+      </c>
+      <c r="C87" s="2">
+        <v>3</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E87" s="2">
+        <v>4</v>
+      </c>
+      <c r="F87" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A88" s="2">
+        <v>40000087</v>
+      </c>
+      <c r="B88" s="2">
+        <v>7</v>
+      </c>
+      <c r="C88" s="2">
+        <v>3</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E88" s="2">
+        <v>4</v>
+      </c>
+      <c r="F88" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A89" s="2">
+        <v>40000088</v>
+      </c>
+      <c r="B89" s="2">
+        <v>7</v>
+      </c>
+      <c r="C89" s="2">
+        <v>4</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E89" s="2">
+        <v>12</v>
+      </c>
+      <c r="F89" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A90" s="2">
+        <v>40000089</v>
+      </c>
+      <c r="B90" s="2">
+        <v>7</v>
+      </c>
+      <c r="C90" s="2">
+        <v>4</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E90" s="2">
+        <v>12</v>
+      </c>
+      <c r="F90" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A91" s="2">
+        <v>40000090</v>
+      </c>
+      <c r="B91" s="2">
+        <v>7</v>
+      </c>
+      <c r="C91" s="2">
+        <v>4</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E91" s="2">
+        <v>4</v>
+      </c>
+      <c r="F91" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A92" s="2">
+        <v>40000091</v>
+      </c>
+      <c r="B92" s="2">
+        <v>7</v>
+      </c>
+      <c r="C92" s="2">
+        <v>4</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E92" s="2">
+        <v>4</v>
+      </c>
+      <c r="F92" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A93" s="2">
+        <v>40000092</v>
+      </c>
+      <c r="B93" s="2">
+        <v>7</v>
+      </c>
+      <c r="C93" s="2">
+        <v>5</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E93" s="2">
+        <v>16</v>
+      </c>
+      <c r="F93" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A94" s="2">
+        <v>40000093</v>
+      </c>
+      <c r="B94" s="2">
+        <v>7</v>
+      </c>
+      <c r="C94" s="2">
+        <v>5</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E94" s="2">
+        <v>16</v>
+      </c>
+      <c r="F94" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A95" s="2">
+        <v>40000094</v>
+      </c>
+      <c r="B95" s="2">
+        <v>7</v>
+      </c>
+      <c r="C95" s="2">
+        <v>5</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E95" s="2">
+        <v>8</v>
+      </c>
+      <c r="F95" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A96" s="2">
+        <v>40000095</v>
+      </c>
+      <c r="B96" s="2">
+        <v>7</v>
+      </c>
+      <c r="C96" s="2">
+        <v>5</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E96" s="2">
+        <v>8</v>
+      </c>
+      <c r="F96" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A97" s="1">
+        <v>40000096</v>
+      </c>
+      <c r="B97" s="1">
+        <v>8</v>
+      </c>
+      <c r="C97" s="1">
+        <v>1</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E97" s="1">
+        <v>6</v>
+      </c>
+      <c r="F97" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A98" s="1">
+        <v>40000097</v>
+      </c>
+      <c r="B98" s="1">
+        <v>8</v>
+      </c>
+      <c r="C98" s="1">
+        <v>1</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E98" s="1">
+        <v>6</v>
+      </c>
+      <c r="F98" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A99" s="1">
+        <v>40000098</v>
+      </c>
+      <c r="B99" s="1">
+        <v>8</v>
+      </c>
+      <c r="C99" s="1">
+        <v>1</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E99" s="1">
+        <v>2</v>
+      </c>
+      <c r="F99" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A100" s="1">
+        <v>40000099</v>
+      </c>
+      <c r="B100" s="1">
+        <v>8</v>
+      </c>
+      <c r="C100" s="1">
+        <v>1</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E100" s="1">
+        <v>2</v>
+      </c>
+      <c r="F100" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A101" s="1">
+        <v>40000100</v>
+      </c>
+      <c r="B101" s="1">
+        <v>8</v>
+      </c>
+      <c r="C101" s="1">
+        <v>2</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E101" s="1">
+        <v>6</v>
+      </c>
+      <c r="F101" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A102" s="1">
+        <v>40000101</v>
+      </c>
+      <c r="B102" s="1">
+        <v>8</v>
+      </c>
+      <c r="C102" s="1">
+        <v>2</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E102" s="1">
+        <v>6</v>
+      </c>
+      <c r="F102" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A103" s="1">
+        <v>40000102</v>
+      </c>
+      <c r="B103" s="1">
+        <v>8</v>
+      </c>
+      <c r="C103" s="1">
+        <v>2</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E103" s="1">
+        <v>2</v>
+      </c>
+      <c r="F103" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A104" s="1">
+        <v>40000103</v>
+      </c>
+      <c r="B104" s="1">
+        <v>8</v>
+      </c>
+      <c r="C104" s="1">
+        <v>2</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E104" s="1">
+        <v>2</v>
+      </c>
+      <c r="F104" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A105" s="1">
+        <v>40000104</v>
+      </c>
+      <c r="B105" s="1">
+        <v>8</v>
+      </c>
+      <c r="C105" s="1">
+        <v>3</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E105" s="1">
+        <v>12</v>
+      </c>
+      <c r="F105" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A106" s="1">
+        <v>40000105</v>
+      </c>
+      <c r="B106" s="1">
+        <v>8</v>
+      </c>
+      <c r="C106" s="1">
+        <v>3</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E106" s="1">
+        <v>12</v>
+      </c>
+      <c r="F106" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A107" s="1">
+        <v>40000106</v>
+      </c>
+      <c r="B107" s="1">
+        <v>8</v>
+      </c>
+      <c r="C107" s="1">
+        <v>3</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E107" s="1">
+        <v>4</v>
+      </c>
+      <c r="F107" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A108" s="1">
+        <v>40000107</v>
+      </c>
+      <c r="B108" s="1">
+        <v>8</v>
+      </c>
+      <c r="C108" s="1">
+        <v>3</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E108" s="1">
+        <v>4</v>
+      </c>
+      <c r="F108" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A109" s="1">
+        <v>40000108</v>
+      </c>
+      <c r="B109" s="1">
+        <v>8</v>
+      </c>
+      <c r="C109" s="1">
+        <v>4</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E109" s="1">
+        <v>12</v>
+      </c>
+      <c r="F109" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A110" s="1">
+        <v>40000109</v>
+      </c>
+      <c r="B110" s="1">
+        <v>8</v>
+      </c>
+      <c r="C110" s="1">
+        <v>4</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E110" s="1">
+        <v>12</v>
+      </c>
+      <c r="F110" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A111" s="1">
+        <v>40000110</v>
+      </c>
+      <c r="B111" s="1">
+        <v>8</v>
+      </c>
+      <c r="C111" s="1">
+        <v>4</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E111" s="1">
+        <v>4</v>
+      </c>
+      <c r="F111" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A112" s="1">
+        <v>40000111</v>
+      </c>
+      <c r="B112" s="1">
+        <v>8</v>
+      </c>
+      <c r="C112" s="1">
+        <v>4</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E112" s="1">
+        <v>4</v>
+      </c>
+      <c r="F112" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A113" s="1">
+        <v>40000112</v>
+      </c>
+      <c r="B113" s="1">
+        <v>8</v>
+      </c>
+      <c r="C113" s="1">
+        <v>5</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E113" s="1">
+        <v>16</v>
+      </c>
+      <c r="F113" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A114" s="1">
+        <v>40000113</v>
+      </c>
+      <c r="B114" s="1">
+        <v>8</v>
+      </c>
+      <c r="C114" s="1">
+        <v>5</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E114" s="1">
+        <v>16</v>
+      </c>
+      <c r="F114" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A115" s="1">
+        <v>40000114</v>
+      </c>
+      <c r="B115" s="1">
+        <v>8</v>
+      </c>
+      <c r="C115" s="1">
+        <v>5</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E115" s="1">
+        <v>8</v>
+      </c>
+      <c r="F115" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A116" s="1">
+        <v>40000115</v>
+      </c>
+      <c r="B116" s="1">
+        <v>8</v>
+      </c>
+      <c r="C116" s="1">
+        <v>5</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E116" s="1">
+        <v>8</v>
+      </c>
+      <c r="F116" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A117" s="2">
+        <v>40000116</v>
+      </c>
+      <c r="B117" s="2">
+        <v>9</v>
+      </c>
+      <c r="C117" s="2">
+        <v>1</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E117" s="2">
+        <v>6</v>
+      </c>
+      <c r="F117" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A118" s="2">
+        <v>40000117</v>
+      </c>
+      <c r="B118" s="2">
+        <v>9</v>
+      </c>
+      <c r="C118" s="2">
+        <v>1</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E118" s="2">
+        <v>6</v>
+      </c>
+      <c r="F118" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A119" s="2">
+        <v>40000118</v>
+      </c>
+      <c r="B119" s="2">
+        <v>9</v>
+      </c>
+      <c r="C119" s="2">
+        <v>1</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E119" s="2">
+        <v>2</v>
+      </c>
+      <c r="F119" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A120" s="2">
+        <v>40000119</v>
+      </c>
+      <c r="B120" s="2">
+        <v>9</v>
+      </c>
+      <c r="C120" s="2">
+        <v>1</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E120" s="2">
+        <v>2</v>
+      </c>
+      <c r="F120" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A121" s="2">
+        <v>40000120</v>
+      </c>
+      <c r="B121" s="2">
+        <v>9</v>
+      </c>
+      <c r="C121" s="2">
+        <v>2</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E121" s="2">
+        <v>6</v>
+      </c>
+      <c r="F121" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A122" s="2">
+        <v>40000121</v>
+      </c>
+      <c r="B122" s="2">
+        <v>9</v>
+      </c>
+      <c r="C122" s="2">
+        <v>2</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E122" s="2">
+        <v>6</v>
+      </c>
+      <c r="F122" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A123" s="2">
+        <v>40000122</v>
+      </c>
+      <c r="B123" s="2">
+        <v>9</v>
+      </c>
+      <c r="C123" s="2">
+        <v>2</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E123" s="2">
+        <v>2</v>
+      </c>
+      <c r="F123" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A124" s="2">
+        <v>40000123</v>
+      </c>
+      <c r="B124" s="2">
+        <v>9</v>
+      </c>
+      <c r="C124" s="2">
+        <v>2</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E124" s="2">
+        <v>2</v>
+      </c>
+      <c r="F124" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A125" s="2">
+        <v>40000124</v>
+      </c>
+      <c r="B125" s="2">
+        <v>9</v>
+      </c>
+      <c r="C125" s="2">
+        <v>3</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E125" s="2">
+        <v>12</v>
+      </c>
+      <c r="F125" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A126" s="2">
+        <v>40000125</v>
+      </c>
+      <c r="B126" s="2">
+        <v>9</v>
+      </c>
+      <c r="C126" s="2">
+        <v>3</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E126" s="2">
+        <v>12</v>
+      </c>
+      <c r="F126" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A127" s="2">
+        <v>40000126</v>
+      </c>
+      <c r="B127" s="2">
+        <v>9</v>
+      </c>
+      <c r="C127" s="2">
+        <v>3</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E127" s="2">
+        <v>4</v>
+      </c>
+      <c r="F127" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A128" s="2">
+        <v>40000127</v>
+      </c>
+      <c r="B128" s="2">
+        <v>9</v>
+      </c>
+      <c r="C128" s="2">
+        <v>3</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E128" s="2">
+        <v>4</v>
+      </c>
+      <c r="F128" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A129" s="2">
+        <v>40000128</v>
+      </c>
+      <c r="B129" s="2">
+        <v>9</v>
+      </c>
+      <c r="C129" s="2">
+        <v>4</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E129" s="2">
+        <v>12</v>
+      </c>
+      <c r="F129" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A130" s="2">
+        <v>40000129</v>
+      </c>
+      <c r="B130" s="2">
+        <v>9</v>
+      </c>
+      <c r="C130" s="2">
+        <v>4</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E130" s="2">
+        <v>12</v>
+      </c>
+      <c r="F130" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A131" s="2">
+        <v>40000130</v>
+      </c>
+      <c r="B131" s="2">
+        <v>9</v>
+      </c>
+      <c r="C131" s="2">
+        <v>4</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E131" s="2">
+        <v>4</v>
+      </c>
+      <c r="F131" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A132" s="2">
+        <v>40000131</v>
+      </c>
+      <c r="B132" s="2">
+        <v>9</v>
+      </c>
+      <c r="C132" s="2">
+        <v>4</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E132" s="2">
+        <v>4</v>
+      </c>
+      <c r="F132" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A133" s="2">
+        <v>40000132</v>
+      </c>
+      <c r="B133" s="2">
+        <v>9</v>
+      </c>
+      <c r="C133" s="2">
+        <v>5</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E133" s="2">
+        <v>16</v>
+      </c>
+      <c r="F133" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A134" s="2">
+        <v>40000133</v>
+      </c>
+      <c r="B134" s="2">
+        <v>9</v>
+      </c>
+      <c r="C134" s="2">
+        <v>5</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E134" s="2">
+        <v>16</v>
+      </c>
+      <c r="F134" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A135" s="2">
+        <v>40000134</v>
+      </c>
+      <c r="B135" s="2">
+        <v>9</v>
+      </c>
+      <c r="C135" s="2">
+        <v>5</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E135" s="2">
+        <v>8</v>
+      </c>
+      <c r="F135" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A136" s="2">
+        <v>40000135</v>
+      </c>
+      <c r="B136" s="2">
+        <v>9</v>
+      </c>
+      <c r="C136" s="2">
+        <v>5</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E136" s="2">
+        <v>8</v>
+      </c>
+      <c r="F136" s="2">
+        <v>120</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B0346D1-7C65-450B-8AE4-EA1E48A5995A}">
+  <dimension ref="A1:F136"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>50000001</v>
+      </c>
+      <c r="B2" s="2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" s="2">
+        <v>8</v>
+      </c>
+      <c r="F2" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>50000002</v>
+      </c>
+      <c r="B3" s="2">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" s="2">
+        <v>8</v>
+      </c>
+      <c r="F3" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>50000003</v>
+      </c>
+      <c r="B4" s="2">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2">
+        <v>2</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="2">
+        <v>8</v>
+      </c>
+      <c r="F4" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>50000004</v>
+      </c>
+      <c r="B5" s="2">
+        <v>1</v>
+      </c>
+      <c r="C5" s="2">
+        <v>2</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="2">
+        <v>8</v>
+      </c>
+      <c r="F5" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>50000005</v>
+      </c>
+      <c r="B6" s="2">
+        <v>1</v>
+      </c>
+      <c r="C6" s="2">
+        <v>3</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="2">
+        <v>16</v>
+      </c>
+      <c r="F6" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>50000006</v>
+      </c>
+      <c r="B7" s="2">
+        <v>1</v>
+      </c>
+      <c r="C7" s="2">
+        <v>3</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="2">
+        <v>16</v>
+      </c>
+      <c r="F7" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>50000007</v>
+      </c>
+      <c r="B8" s="2">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2">
+        <v>4</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="2">
+        <v>16</v>
+      </c>
+      <c r="F8" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>50000008</v>
+      </c>
+      <c r="B9" s="2">
+        <v>1</v>
+      </c>
+      <c r="C9" s="2">
+        <v>4</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="2">
+        <v>16</v>
+      </c>
+      <c r="F9" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>50000009</v>
+      </c>
+      <c r="B10" s="2">
+        <v>1</v>
+      </c>
+      <c r="C10" s="2">
+        <v>5</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="2">
+        <v>24</v>
+      </c>
+      <c r="F10" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>50000010</v>
+      </c>
+      <c r="B11" s="2">
+        <v>1</v>
+      </c>
+      <c r="C11" s="2">
+        <v>5</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="2">
+        <v>24</v>
+      </c>
+      <c r="F11" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>50000011</v>
+      </c>
+      <c r="B12" s="1">
+        <v>2</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" s="1">
+        <v>8</v>
+      </c>
+      <c r="F12" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>50000012</v>
+      </c>
+      <c r="B13" s="1">
+        <v>2</v>
+      </c>
+      <c r="C13" s="1">
+        <v>1</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="1">
+        <v>8</v>
+      </c>
+      <c r="F13" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <v>50000013</v>
+      </c>
+      <c r="B14" s="1">
+        <v>2</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" s="1">
+        <v>8</v>
+      </c>
+      <c r="F14" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>50000014</v>
+      </c>
+      <c r="B15" s="1">
+        <v>2</v>
+      </c>
+      <c r="C15" s="1">
+        <v>2</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" s="1">
+        <v>8</v>
+      </c>
+      <c r="F15" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>50000015</v>
+      </c>
+      <c r="B16" s="1">
+        <v>2</v>
+      </c>
+      <c r="C16" s="1">
+        <v>3</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E16" s="1">
+        <v>16</v>
+      </c>
+      <c r="F16" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>50000016</v>
+      </c>
+      <c r="B17" s="1">
+        <v>2</v>
+      </c>
+      <c r="C17" s="1">
+        <v>3</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" s="1">
+        <v>16</v>
+      </c>
+      <c r="F17" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>50000017</v>
+      </c>
+      <c r="B18" s="1">
+        <v>2</v>
+      </c>
+      <c r="C18" s="1">
+        <v>4</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E18" s="1">
+        <v>16</v>
+      </c>
+      <c r="F18" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <v>50000018</v>
+      </c>
+      <c r="B19" s="1">
+        <v>2</v>
+      </c>
+      <c r="C19" s="1">
+        <v>4</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E19" s="1">
+        <v>16</v>
+      </c>
+      <c r="F19" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <v>50000019</v>
+      </c>
+      <c r="B20" s="1">
+        <v>2</v>
+      </c>
+      <c r="C20" s="1">
+        <v>5</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E20" s="1">
+        <v>24</v>
+      </c>
+      <c r="F20" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <v>50000020</v>
+      </c>
+      <c r="B21" s="1">
+        <v>2</v>
+      </c>
+      <c r="C21" s="1">
+        <v>5</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E21" s="1">
+        <v>24</v>
+      </c>
+      <c r="F21" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="2">
+        <v>50000021</v>
+      </c>
+      <c r="B22" s="2">
+        <v>3</v>
+      </c>
+      <c r="C22" s="2">
+        <v>1</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22" s="2">
+        <v>8</v>
+      </c>
+      <c r="F22" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="2">
+        <v>50000022</v>
+      </c>
+      <c r="B23" s="2">
+        <v>3</v>
+      </c>
+      <c r="C23" s="2">
+        <v>1</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E23" s="2">
+        <v>8</v>
+      </c>
+      <c r="F23" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="2">
+        <v>50000023</v>
+      </c>
+      <c r="B24" s="2">
+        <v>3</v>
+      </c>
+      <c r="C24" s="2">
+        <v>2</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E24" s="2">
+        <v>8</v>
+      </c>
+      <c r="F24" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="2">
+        <v>50000024</v>
+      </c>
+      <c r="B25" s="2">
+        <v>3</v>
+      </c>
+      <c r="C25" s="2">
+        <v>2</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E25" s="2">
+        <v>8</v>
+      </c>
+      <c r="F25" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="2">
+        <v>50000025</v>
+      </c>
+      <c r="B26" s="2">
+        <v>3</v>
+      </c>
+      <c r="C26" s="2">
+        <v>3</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E26" s="2">
+        <v>16</v>
+      </c>
+      <c r="F26" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="2">
+        <v>50000026</v>
+      </c>
+      <c r="B27" s="2">
+        <v>3</v>
+      </c>
+      <c r="C27" s="2">
+        <v>3</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E27" s="2">
+        <v>16</v>
+      </c>
+      <c r="F27" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="2">
+        <v>50000027</v>
+      </c>
+      <c r="B28" s="2">
+        <v>3</v>
+      </c>
+      <c r="C28" s="2">
+        <v>4</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E28" s="2">
+        <v>16</v>
+      </c>
+      <c r="F28" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="2">
+        <v>50000028</v>
+      </c>
+      <c r="B29" s="2">
+        <v>3</v>
+      </c>
+      <c r="C29" s="2">
+        <v>4</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E29" s="2">
+        <v>16</v>
+      </c>
+      <c r="F29" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="2">
+        <v>50000029</v>
+      </c>
+      <c r="B30" s="2">
+        <v>3</v>
+      </c>
+      <c r="C30" s="2">
+        <v>5</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E30" s="2">
+        <v>24</v>
+      </c>
+      <c r="F30" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="2">
+        <v>50000030</v>
+      </c>
+      <c r="B31" s="2">
+        <v>3</v>
+      </c>
+      <c r="C31" s="2">
+        <v>5</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E31" s="2">
+        <v>24</v>
+      </c>
+      <c r="F31" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <v>50000031</v>
+      </c>
+      <c r="B32" s="1">
+        <v>4</v>
+      </c>
+      <c r="C32" s="1">
+        <v>1</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E32" s="1">
+        <v>6</v>
+      </c>
+      <c r="F32" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
+        <v>50000032</v>
+      </c>
+      <c r="B33" s="1">
+        <v>4</v>
+      </c>
+      <c r="C33" s="1">
+        <v>1</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E33" s="1">
+        <v>6</v>
+      </c>
+      <c r="F33" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <v>50000033</v>
+      </c>
+      <c r="B34" s="1">
+        <v>4</v>
+      </c>
+      <c r="C34" s="1">
+        <v>1</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E34" s="1">
+        <v>4</v>
+      </c>
+      <c r="F34" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <v>50000034</v>
+      </c>
+      <c r="B35" s="1">
+        <v>4</v>
+      </c>
+      <c r="C35" s="1">
+        <v>2</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E35" s="1">
+        <v>6</v>
+      </c>
+      <c r="F35" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="1">
+        <v>50000035</v>
+      </c>
+      <c r="B36" s="1">
+        <v>4</v>
+      </c>
+      <c r="C36" s="1">
+        <v>2</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E36" s="1">
+        <v>6</v>
+      </c>
+      <c r="F36" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <v>50000036</v>
+      </c>
+      <c r="B37" s="1">
+        <v>4</v>
+      </c>
+      <c r="C37" s="1">
+        <v>2</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E37" s="1">
+        <v>4</v>
+      </c>
+      <c r="F37" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="1">
+        <v>50000037</v>
+      </c>
+      <c r="B38" s="1">
+        <v>4</v>
+      </c>
+      <c r="C38" s="1">
+        <v>3</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E38" s="1">
+        <v>12</v>
+      </c>
+      <c r="F38" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
+        <v>50000038</v>
+      </c>
+      <c r="B39" s="1">
+        <v>4</v>
+      </c>
+      <c r="C39" s="1">
+        <v>3</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E39" s="1">
+        <v>12</v>
+      </c>
+      <c r="F39" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="1">
+        <v>50000039</v>
+      </c>
+      <c r="B40" s="1">
+        <v>4</v>
+      </c>
+      <c r="C40" s="1">
+        <v>3</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E40" s="1">
+        <v>8</v>
+      </c>
+      <c r="F40" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="1">
+        <v>50000040</v>
+      </c>
+      <c r="B41" s="1">
+        <v>4</v>
+      </c>
+      <c r="C41" s="1">
+        <v>4</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E41" s="1">
+        <v>12</v>
+      </c>
+      <c r="F41" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="1">
+        <v>50000041</v>
+      </c>
+      <c r="B42" s="1">
+        <v>4</v>
+      </c>
+      <c r="C42" s="1">
+        <v>4</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E42" s="1">
+        <v>12</v>
+      </c>
+      <c r="F42" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="1">
+        <v>50000042</v>
+      </c>
+      <c r="B43" s="1">
+        <v>4</v>
+      </c>
+      <c r="C43" s="1">
+        <v>4</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E43" s="1">
+        <v>8</v>
+      </c>
+      <c r="F43" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="1">
+        <v>50000043</v>
+      </c>
+      <c r="B44" s="1">
+        <v>4</v>
+      </c>
+      <c r="C44" s="1">
+        <v>5</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E44" s="1">
+        <v>16</v>
+      </c>
+      <c r="F44" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" s="1">
+        <v>50000044</v>
+      </c>
+      <c r="B45" s="1">
+        <v>4</v>
+      </c>
+      <c r="C45" s="1">
+        <v>5</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E45" s="1">
+        <v>16</v>
+      </c>
+      <c r="F45" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" s="1">
+        <v>50000045</v>
+      </c>
+      <c r="B46" s="1">
+        <v>4</v>
+      </c>
+      <c r="C46" s="1">
+        <v>5</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E46" s="1">
+        <v>12</v>
+      </c>
+      <c r="F46" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" s="2">
+        <v>50000046</v>
+      </c>
+      <c r="B47" s="2">
+        <v>5</v>
+      </c>
+      <c r="C47" s="2">
+        <v>1</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E47" s="2">
+        <v>6</v>
+      </c>
+      <c r="F47" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="2">
+        <v>50000047</v>
+      </c>
+      <c r="B48" s="2">
+        <v>5</v>
+      </c>
+      <c r="C48" s="2">
+        <v>1</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E48" s="2">
+        <v>6</v>
+      </c>
+      <c r="F48" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" s="2">
+        <v>50000048</v>
+      </c>
+      <c r="B49" s="2">
+        <v>5</v>
+      </c>
+      <c r="C49" s="2">
+        <v>1</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E49" s="2">
+        <v>4</v>
+      </c>
+      <c r="F49" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" s="2">
+        <v>50000049</v>
+      </c>
+      <c r="B50" s="2">
+        <v>5</v>
+      </c>
+      <c r="C50" s="2">
+        <v>2</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E50" s="2">
+        <v>6</v>
+      </c>
+      <c r="F50" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" s="2">
+        <v>50000050</v>
+      </c>
+      <c r="B51" s="2">
+        <v>5</v>
+      </c>
+      <c r="C51" s="2">
+        <v>2</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E51" s="2">
+        <v>6</v>
+      </c>
+      <c r="F51" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" s="2">
+        <v>50000051</v>
+      </c>
+      <c r="B52" s="2">
+        <v>5</v>
+      </c>
+      <c r="C52" s="2">
+        <v>2</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E52" s="2">
+        <v>4</v>
+      </c>
+      <c r="F52" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53" s="2">
+        <v>50000052</v>
+      </c>
+      <c r="B53" s="2">
+        <v>5</v>
+      </c>
+      <c r="C53" s="2">
+        <v>3</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E53" s="2">
+        <v>12</v>
+      </c>
+      <c r="F53" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54" s="2">
+        <v>50000053</v>
+      </c>
+      <c r="B54" s="2">
+        <v>5</v>
+      </c>
+      <c r="C54" s="2">
+        <v>3</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E54" s="2">
+        <v>12</v>
+      </c>
+      <c r="F54" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55" s="2">
+        <v>50000054</v>
+      </c>
+      <c r="B55" s="2">
+        <v>5</v>
+      </c>
+      <c r="C55" s="2">
+        <v>3</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E55" s="2">
+        <v>8</v>
+      </c>
+      <c r="F55" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56" s="2">
+        <v>50000055</v>
+      </c>
+      <c r="B56" s="2">
+        <v>5</v>
+      </c>
+      <c r="C56" s="2">
+        <v>4</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E56" s="2">
+        <v>12</v>
+      </c>
+      <c r="F56" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57" s="2">
+        <v>50000056</v>
+      </c>
+      <c r="B57" s="2">
+        <v>5</v>
+      </c>
+      <c r="C57" s="2">
+        <v>4</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E57" s="2">
+        <v>12</v>
+      </c>
+      <c r="F57" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A58" s="2">
+        <v>50000057</v>
+      </c>
+      <c r="B58" s="2">
+        <v>5</v>
+      </c>
+      <c r="C58" s="2">
+        <v>4</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E58" s="2">
+        <v>8</v>
+      </c>
+      <c r="F58" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A59" s="2">
+        <v>50000058</v>
+      </c>
+      <c r="B59" s="2">
+        <v>5</v>
+      </c>
+      <c r="C59" s="2">
+        <v>5</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E59" s="2">
+        <v>16</v>
+      </c>
+      <c r="F59" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60" s="2">
+        <v>50000059</v>
+      </c>
+      <c r="B60" s="2">
+        <v>5</v>
+      </c>
+      <c r="C60" s="2">
+        <v>5</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E60" s="2">
+        <v>16</v>
+      </c>
+      <c r="F60" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A61" s="2">
+        <v>50000060</v>
+      </c>
+      <c r="B61" s="2">
+        <v>5</v>
+      </c>
+      <c r="C61" s="2">
+        <v>5</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E61" s="2">
+        <v>12</v>
+      </c>
+      <c r="F61" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A62" s="1">
+        <v>50000061</v>
+      </c>
+      <c r="B62" s="1">
+        <v>6</v>
+      </c>
+      <c r="C62" s="1">
+        <v>1</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E62" s="1">
+        <v>6</v>
+      </c>
+      <c r="F62" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A63" s="1">
+        <v>50000062</v>
+      </c>
+      <c r="B63" s="1">
+        <v>6</v>
+      </c>
+      <c r="C63" s="1">
+        <v>1</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E63" s="1">
+        <v>6</v>
+      </c>
+      <c r="F63" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A64" s="1">
+        <v>50000063</v>
+      </c>
+      <c r="B64" s="1">
+        <v>6</v>
+      </c>
+      <c r="C64" s="1">
+        <v>1</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E64" s="1">
+        <v>4</v>
+      </c>
+      <c r="F64" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A65" s="1">
+        <v>50000064</v>
+      </c>
+      <c r="B65" s="1">
+        <v>6</v>
+      </c>
+      <c r="C65" s="1">
+        <v>2</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E65" s="1">
+        <v>6</v>
+      </c>
+      <c r="F65" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A66" s="1">
+        <v>50000065</v>
+      </c>
+      <c r="B66" s="1">
+        <v>6</v>
+      </c>
+      <c r="C66" s="1">
+        <v>2</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E66" s="1">
+        <v>6</v>
+      </c>
+      <c r="F66" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A67" s="1">
+        <v>50000066</v>
+      </c>
+      <c r="B67" s="1">
+        <v>6</v>
+      </c>
+      <c r="C67" s="1">
+        <v>2</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E67" s="1">
+        <v>4</v>
+      </c>
+      <c r="F67" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A68" s="1">
+        <v>50000067</v>
+      </c>
+      <c r="B68" s="1">
+        <v>6</v>
+      </c>
+      <c r="C68" s="1">
+        <v>3</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E68" s="1">
+        <v>12</v>
+      </c>
+      <c r="F68" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A69" s="1">
+        <v>50000068</v>
+      </c>
+      <c r="B69" s="1">
+        <v>6</v>
+      </c>
+      <c r="C69" s="1">
+        <v>3</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E69" s="1">
+        <v>12</v>
+      </c>
+      <c r="F69" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A70" s="1">
+        <v>50000069</v>
+      </c>
+      <c r="B70" s="1">
+        <v>6</v>
+      </c>
+      <c r="C70" s="1">
+        <v>3</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E70" s="1">
+        <v>8</v>
+      </c>
+      <c r="F70" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A71" s="1">
+        <v>50000070</v>
+      </c>
+      <c r="B71" s="1">
+        <v>6</v>
+      </c>
+      <c r="C71" s="1">
+        <v>4</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E71" s="1">
+        <v>12</v>
+      </c>
+      <c r="F71" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A72" s="1">
+        <v>50000071</v>
+      </c>
+      <c r="B72" s="1">
+        <v>6</v>
+      </c>
+      <c r="C72" s="1">
+        <v>4</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E72" s="1">
+        <v>12</v>
+      </c>
+      <c r="F72" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A73" s="1">
+        <v>50000072</v>
+      </c>
+      <c r="B73" s="1">
+        <v>6</v>
+      </c>
+      <c r="C73" s="1">
+        <v>4</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E73" s="1">
+        <v>8</v>
+      </c>
+      <c r="F73" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A74" s="1">
+        <v>50000073</v>
+      </c>
+      <c r="B74" s="1">
+        <v>6</v>
+      </c>
+      <c r="C74" s="1">
+        <v>5</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E74" s="1">
+        <v>16</v>
+      </c>
+      <c r="F74" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A75" s="1">
+        <v>50000074</v>
+      </c>
+      <c r="B75" s="1">
+        <v>6</v>
+      </c>
+      <c r="C75" s="1">
+        <v>5</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E75" s="1">
+        <v>16</v>
+      </c>
+      <c r="F75" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A76" s="1">
+        <v>50000075</v>
+      </c>
+      <c r="B76" s="1">
+        <v>6</v>
+      </c>
+      <c r="C76" s="1">
+        <v>5</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E76" s="1">
+        <v>12</v>
+      </c>
+      <c r="F76" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A77" s="2">
+        <v>50000076</v>
+      </c>
+      <c r="B77" s="2">
+        <v>7</v>
+      </c>
+      <c r="C77" s="2">
+        <v>1</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E77" s="2">
+        <v>6</v>
+      </c>
+      <c r="F77" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A78" s="2">
+        <v>50000077</v>
+      </c>
+      <c r="B78" s="2">
+        <v>7</v>
+      </c>
+      <c r="C78" s="2">
+        <v>1</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E78" s="2">
+        <v>6</v>
+      </c>
+      <c r="F78" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A79" s="2">
+        <v>50000078</v>
+      </c>
+      <c r="B79" s="2">
+        <v>7</v>
+      </c>
+      <c r="C79" s="2">
+        <v>1</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E79" s="2">
+        <v>2</v>
+      </c>
+      <c r="F79" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A80" s="2">
+        <v>50000079</v>
+      </c>
+      <c r="B80" s="2">
+        <v>7</v>
+      </c>
+      <c r="C80" s="2">
+        <v>1</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E80" s="2">
+        <v>2</v>
+      </c>
+      <c r="F80" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A81" s="2">
+        <v>50000080</v>
+      </c>
+      <c r="B81" s="2">
+        <v>7</v>
+      </c>
+      <c r="C81" s="2">
+        <v>2</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E81" s="2">
+        <v>6</v>
+      </c>
+      <c r="F81" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A82" s="2">
+        <v>50000081</v>
+      </c>
+      <c r="B82" s="2">
+        <v>7</v>
+      </c>
+      <c r="C82" s="2">
+        <v>2</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E82" s="2">
+        <v>6</v>
+      </c>
+      <c r="F82" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A83" s="2">
+        <v>50000082</v>
+      </c>
+      <c r="B83" s="2">
+        <v>7</v>
+      </c>
+      <c r="C83" s="2">
+        <v>2</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E83" s="2">
+        <v>2</v>
+      </c>
+      <c r="F83" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A84" s="2">
+        <v>50000083</v>
+      </c>
+      <c r="B84" s="2">
+        <v>7</v>
+      </c>
+      <c r="C84" s="2">
+        <v>2</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E84" s="2">
+        <v>2</v>
+      </c>
+      <c r="F84" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A85" s="2">
+        <v>50000084</v>
+      </c>
+      <c r="B85" s="2">
+        <v>7</v>
+      </c>
+      <c r="C85" s="2">
+        <v>3</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E85" s="2">
+        <v>12</v>
+      </c>
+      <c r="F85" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A86" s="2">
+        <v>50000085</v>
+      </c>
+      <c r="B86" s="2">
+        <v>7</v>
+      </c>
+      <c r="C86" s="2">
+        <v>3</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E86" s="2">
+        <v>12</v>
+      </c>
+      <c r="F86" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A87" s="2">
+        <v>50000086</v>
+      </c>
+      <c r="B87" s="2">
+        <v>7</v>
+      </c>
+      <c r="C87" s="2">
+        <v>3</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E87" s="2">
+        <v>4</v>
+      </c>
+      <c r="F87" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A88" s="2">
+        <v>50000087</v>
+      </c>
+      <c r="B88" s="2">
+        <v>7</v>
+      </c>
+      <c r="C88" s="2">
+        <v>3</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E88" s="2">
+        <v>4</v>
+      </c>
+      <c r="F88" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A89" s="2">
+        <v>50000088</v>
+      </c>
+      <c r="B89" s="2">
+        <v>7</v>
+      </c>
+      <c r="C89" s="2">
+        <v>4</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E89" s="2">
+        <v>12</v>
+      </c>
+      <c r="F89" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A90" s="2">
+        <v>50000089</v>
+      </c>
+      <c r="B90" s="2">
+        <v>7</v>
+      </c>
+      <c r="C90" s="2">
+        <v>4</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E90" s="2">
+        <v>12</v>
+      </c>
+      <c r="F90" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A91" s="2">
+        <v>50000090</v>
+      </c>
+      <c r="B91" s="2">
+        <v>7</v>
+      </c>
+      <c r="C91" s="2">
+        <v>4</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E91" s="2">
+        <v>4</v>
+      </c>
+      <c r="F91" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A92" s="2">
+        <v>50000091</v>
+      </c>
+      <c r="B92" s="2">
+        <v>7</v>
+      </c>
+      <c r="C92" s="2">
+        <v>4</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E92" s="2">
+        <v>4</v>
+      </c>
+      <c r="F92" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A93" s="2">
+        <v>50000092</v>
+      </c>
+      <c r="B93" s="2">
+        <v>7</v>
+      </c>
+      <c r="C93" s="2">
+        <v>5</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E93" s="2">
+        <v>16</v>
+      </c>
+      <c r="F93" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A94" s="2">
+        <v>50000093</v>
+      </c>
+      <c r="B94" s="2">
+        <v>7</v>
+      </c>
+      <c r="C94" s="2">
+        <v>5</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E94" s="2">
+        <v>16</v>
+      </c>
+      <c r="F94" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A95" s="2">
+        <v>50000094</v>
+      </c>
+      <c r="B95" s="2">
+        <v>7</v>
+      </c>
+      <c r="C95" s="2">
+        <v>5</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E95" s="2">
+        <v>8</v>
+      </c>
+      <c r="F95" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A96" s="2">
+        <v>50000095</v>
+      </c>
+      <c r="B96" s="2">
+        <v>7</v>
+      </c>
+      <c r="C96" s="2">
+        <v>5</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E96" s="2">
+        <v>8</v>
+      </c>
+      <c r="F96" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A97" s="1">
+        <v>50000096</v>
+      </c>
+      <c r="B97" s="1">
+        <v>8</v>
+      </c>
+      <c r="C97" s="1">
+        <v>1</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E97" s="1">
+        <v>6</v>
+      </c>
+      <c r="F97" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A98" s="1">
+        <v>50000097</v>
+      </c>
+      <c r="B98" s="1">
+        <v>8</v>
+      </c>
+      <c r="C98" s="1">
+        <v>1</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E98" s="1">
+        <v>6</v>
+      </c>
+      <c r="F98" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A99" s="1">
+        <v>50000098</v>
+      </c>
+      <c r="B99" s="1">
+        <v>8</v>
+      </c>
+      <c r="C99" s="1">
+        <v>1</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E99" s="1">
+        <v>2</v>
+      </c>
+      <c r="F99" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A100" s="1">
+        <v>50000099</v>
+      </c>
+      <c r="B100" s="1">
+        <v>8</v>
+      </c>
+      <c r="C100" s="1">
+        <v>1</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E100" s="1">
+        <v>2</v>
+      </c>
+      <c r="F100" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A101" s="1">
+        <v>50000100</v>
+      </c>
+      <c r="B101" s="1">
+        <v>8</v>
+      </c>
+      <c r="C101" s="1">
+        <v>2</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E101" s="1">
+        <v>6</v>
+      </c>
+      <c r="F101" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A102" s="1">
+        <v>50000101</v>
+      </c>
+      <c r="B102" s="1">
+        <v>8</v>
+      </c>
+      <c r="C102" s="1">
+        <v>2</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E102" s="1">
+        <v>6</v>
+      </c>
+      <c r="F102" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A103" s="1">
+        <v>50000102</v>
+      </c>
+      <c r="B103" s="1">
+        <v>8</v>
+      </c>
+      <c r="C103" s="1">
+        <v>2</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E103" s="1">
+        <v>2</v>
+      </c>
+      <c r="F103" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A104" s="1">
+        <v>50000103</v>
+      </c>
+      <c r="B104" s="1">
+        <v>8</v>
+      </c>
+      <c r="C104" s="1">
+        <v>2</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E104" s="1">
+        <v>2</v>
+      </c>
+      <c r="F104" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A105" s="1">
+        <v>50000104</v>
+      </c>
+      <c r="B105" s="1">
+        <v>8</v>
+      </c>
+      <c r="C105" s="1">
+        <v>3</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E105" s="1">
+        <v>12</v>
+      </c>
+      <c r="F105" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A106" s="1">
+        <v>50000105</v>
+      </c>
+      <c r="B106" s="1">
+        <v>8</v>
+      </c>
+      <c r="C106" s="1">
+        <v>3</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E106" s="1">
+        <v>12</v>
+      </c>
+      <c r="F106" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A107" s="1">
+        <v>50000106</v>
+      </c>
+      <c r="B107" s="1">
+        <v>8</v>
+      </c>
+      <c r="C107" s="1">
+        <v>3</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E107" s="1">
+        <v>4</v>
+      </c>
+      <c r="F107" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A108" s="1">
+        <v>50000107</v>
+      </c>
+      <c r="B108" s="1">
+        <v>8</v>
+      </c>
+      <c r="C108" s="1">
+        <v>3</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E108" s="1">
+        <v>4</v>
+      </c>
+      <c r="F108" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A109" s="1">
+        <v>50000108</v>
+      </c>
+      <c r="B109" s="1">
+        <v>8</v>
+      </c>
+      <c r="C109" s="1">
+        <v>4</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E109" s="1">
+        <v>12</v>
+      </c>
+      <c r="F109" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A110" s="1">
+        <v>50000109</v>
+      </c>
+      <c r="B110" s="1">
+        <v>8</v>
+      </c>
+      <c r="C110" s="1">
+        <v>4</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E110" s="1">
+        <v>12</v>
+      </c>
+      <c r="F110" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A111" s="1">
+        <v>50000110</v>
+      </c>
+      <c r="B111" s="1">
+        <v>8</v>
+      </c>
+      <c r="C111" s="1">
+        <v>4</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E111" s="1">
+        <v>4</v>
+      </c>
+      <c r="F111" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A112" s="1">
+        <v>50000111</v>
+      </c>
+      <c r="B112" s="1">
+        <v>8</v>
+      </c>
+      <c r="C112" s="1">
+        <v>4</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E112" s="1">
+        <v>4</v>
+      </c>
+      <c r="F112" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A113" s="1">
+        <v>50000112</v>
+      </c>
+      <c r="B113" s="1">
+        <v>8</v>
+      </c>
+      <c r="C113" s="1">
+        <v>5</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E113" s="1">
+        <v>16</v>
+      </c>
+      <c r="F113" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A114" s="1">
+        <v>50000113</v>
+      </c>
+      <c r="B114" s="1">
+        <v>8</v>
+      </c>
+      <c r="C114" s="1">
+        <v>5</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E114" s="1">
+        <v>16</v>
+      </c>
+      <c r="F114" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A115" s="1">
+        <v>50000114</v>
+      </c>
+      <c r="B115" s="1">
+        <v>8</v>
+      </c>
+      <c r="C115" s="1">
+        <v>5</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E115" s="1">
+        <v>8</v>
+      </c>
+      <c r="F115" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A116" s="1">
+        <v>50000115</v>
+      </c>
+      <c r="B116" s="1">
+        <v>8</v>
+      </c>
+      <c r="C116" s="1">
+        <v>5</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E116" s="1">
+        <v>8</v>
+      </c>
+      <c r="F116" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A117" s="2">
+        <v>50000116</v>
+      </c>
+      <c r="B117" s="2">
+        <v>9</v>
+      </c>
+      <c r="C117" s="2">
+        <v>1</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E117" s="2">
+        <v>6</v>
+      </c>
+      <c r="F117" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A118" s="2">
+        <v>50000117</v>
+      </c>
+      <c r="B118" s="2">
+        <v>9</v>
+      </c>
+      <c r="C118" s="2">
+        <v>1</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E118" s="2">
+        <v>6</v>
+      </c>
+      <c r="F118" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A119" s="2">
+        <v>50000118</v>
+      </c>
+      <c r="B119" s="2">
+        <v>9</v>
+      </c>
+      <c r="C119" s="2">
+        <v>1</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E119" s="2">
+        <v>2</v>
+      </c>
+      <c r="F119" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A120" s="2">
+        <v>50000119</v>
+      </c>
+      <c r="B120" s="2">
+        <v>9</v>
+      </c>
+      <c r="C120" s="2">
+        <v>1</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E120" s="2">
+        <v>2</v>
+      </c>
+      <c r="F120" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A121" s="2">
+        <v>50000120</v>
+      </c>
+      <c r="B121" s="2">
+        <v>9</v>
+      </c>
+      <c r="C121" s="2">
+        <v>2</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E121" s="2">
+        <v>6</v>
+      </c>
+      <c r="F121" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A122" s="2">
+        <v>50000121</v>
+      </c>
+      <c r="B122" s="2">
+        <v>9</v>
+      </c>
+      <c r="C122" s="2">
+        <v>2</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E122" s="2">
+        <v>6</v>
+      </c>
+      <c r="F122" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A123" s="2">
+        <v>50000122</v>
+      </c>
+      <c r="B123" s="2">
+        <v>9</v>
+      </c>
+      <c r="C123" s="2">
+        <v>2</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E123" s="2">
+        <v>2</v>
+      </c>
+      <c r="F123" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A124" s="2">
+        <v>50000123</v>
+      </c>
+      <c r="B124" s="2">
+        <v>9</v>
+      </c>
+      <c r="C124" s="2">
+        <v>2</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E124" s="2">
+        <v>2</v>
+      </c>
+      <c r="F124" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A125" s="2">
+        <v>50000124</v>
+      </c>
+      <c r="B125" s="2">
+        <v>9</v>
+      </c>
+      <c r="C125" s="2">
+        <v>3</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E125" s="2">
+        <v>12</v>
+      </c>
+      <c r="F125" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A126" s="2">
+        <v>50000125</v>
+      </c>
+      <c r="B126" s="2">
+        <v>9</v>
+      </c>
+      <c r="C126" s="2">
+        <v>3</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E126" s="2">
+        <v>12</v>
+      </c>
+      <c r="F126" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A127" s="2">
+        <v>50000126</v>
+      </c>
+      <c r="B127" s="2">
+        <v>9</v>
+      </c>
+      <c r="C127" s="2">
+        <v>3</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E127" s="2">
+        <v>4</v>
+      </c>
+      <c r="F127" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A128" s="2">
+        <v>50000127</v>
+      </c>
+      <c r="B128" s="2">
+        <v>9</v>
+      </c>
+      <c r="C128" s="2">
+        <v>3</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E128" s="2">
+        <v>4</v>
+      </c>
+      <c r="F128" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A129" s="2">
+        <v>50000128</v>
+      </c>
+      <c r="B129" s="2">
+        <v>9</v>
+      </c>
+      <c r="C129" s="2">
+        <v>4</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E129" s="2">
+        <v>12</v>
+      </c>
+      <c r="F129" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A130" s="2">
+        <v>50000129</v>
+      </c>
+      <c r="B130" s="2">
+        <v>9</v>
+      </c>
+      <c r="C130" s="2">
+        <v>4</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E130" s="2">
+        <v>12</v>
+      </c>
+      <c r="F130" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A131" s="2">
+        <v>50000130</v>
+      </c>
+      <c r="B131" s="2">
+        <v>9</v>
+      </c>
+      <c r="C131" s="2">
+        <v>4</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E131" s="2">
+        <v>4</v>
+      </c>
+      <c r="F131" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A132" s="2">
+        <v>50000131</v>
+      </c>
+      <c r="B132" s="2">
+        <v>9</v>
+      </c>
+      <c r="C132" s="2">
+        <v>4</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E132" s="2">
+        <v>4</v>
+      </c>
+      <c r="F132" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A133" s="2">
+        <v>50000132</v>
+      </c>
+      <c r="B133" s="2">
+        <v>9</v>
+      </c>
+      <c r="C133" s="2">
+        <v>5</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E133" s="2">
+        <v>16</v>
+      </c>
+      <c r="F133" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A134" s="2">
+        <v>50000133</v>
+      </c>
+      <c r="B134" s="2">
+        <v>9</v>
+      </c>
+      <c r="C134" s="2">
+        <v>5</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E134" s="2">
+        <v>16</v>
+      </c>
+      <c r="F134" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A135" s="2">
+        <v>50000134</v>
+      </c>
+      <c r="B135" s="2">
+        <v>9</v>
+      </c>
+      <c r="C135" s="2">
+        <v>5</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E135" s="2">
+        <v>8</v>
+      </c>
+      <c r="F135" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A136" s="2">
+        <v>50000135</v>
+      </c>
+      <c r="B136" s="2">
+        <v>9</v>
+      </c>
+      <c r="C136" s="2">
+        <v>5</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="E136" s="2">
         <v>8</v>
